--- a/servers/maze_main_server/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E309A053-CC90-468C-8698-EB92CEE9F53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18282645-7DC2-4691-A99A-DE806F821AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -540,7 +540,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="193">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -902,9 +902,6 @@
     <t>人偶版出售后得到货币的ID</t>
   </si>
   <si>
-    <t>items_atlas_0</t>
-  </si>
-  <si>
     <t>common_ui_atlas_0</t>
   </si>
   <si>
@@ -921,9 +918,6 @@
   </si>
   <si>
     <t>wz_bg_03</t>
-  </si>
-  <si>
-    <t>items_1_atlas_0</t>
   </si>
   <si>
     <t>资源</t>
@@ -1109,6 +1103,33 @@
   </si>
   <si>
     <t>累计经验提高能力等级</t>
+  </si>
+  <si>
+    <t>三选一道具</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得一次三选一</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能道具2</t>
+  </si>
+  <si>
+    <t>技能道具3</t>
+  </si>
+  <si>
+    <t>技能道具4</t>
+  </si>
+  <si>
+    <t>技能道具5</t>
+  </si>
+  <si>
+    <t>技能道具6</t>
+  </si>
+  <si>
+    <t>items_atlas0</t>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1659,7 +1680,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:BF72"/>
+  <dimension ref="A1:BF79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" bestFit="1" customWidth="1"/>
@@ -2063,7 +2084,7 @@
         <v>10</v>
       </c>
       <c r="BF2" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:58" x14ac:dyDescent="0.15">
@@ -2239,7 +2260,7 @@
         <v>72</v>
       </c>
       <c r="BF3" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:58" x14ac:dyDescent="0.15">
@@ -2415,7 +2436,7 @@
         <v>98</v>
       </c>
       <c r="BF4" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:58" x14ac:dyDescent="0.15">
@@ -2429,13 +2450,13 @@
         <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
@@ -2443,23 +2464,23 @@
       <c r="H5" s="1">
         <v>0</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K5" s="1">
         <v>1</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O5" s="1">
         <v>0</v>
@@ -2486,10 +2507,10 @@
         <v>0</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y5" s="1">
         <v>0</v>
@@ -2552,7 +2573,7 @@
         <v>0</v>
       </c>
       <c r="AS5" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT5" s="1">
         <v>0</v>
@@ -2573,7 +2594,7 @@
         <v>0</v>
       </c>
       <c r="AZ5" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA5" s="1">
         <v>0</v>
@@ -2585,7 +2606,7 @@
         <v>0</v>
       </c>
       <c r="BD5" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE5" s="1">
         <v>0</v>
@@ -2605,13 +2626,13 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -2619,23 +2640,23 @@
       <c r="H6" s="1">
         <v>0</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K6" s="1">
         <v>1</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -2662,10 +2683,10 @@
         <v>0</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y6" s="1">
         <v>0</v>
@@ -2728,7 +2749,7 @@
         <v>0</v>
       </c>
       <c r="AS6" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT6" s="1">
         <v>0</v>
@@ -2749,7 +2770,7 @@
         <v>0</v>
       </c>
       <c r="AZ6" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA6" s="1">
         <v>0</v>
@@ -2761,7 +2782,7 @@
         <v>0</v>
       </c>
       <c r="BD6" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE6" s="1">
         <v>0</v>
@@ -2781,13 +2802,13 @@
         <v>4</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -2795,23 +2816,23 @@
       <c r="H7" s="1">
         <v>0</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K7" s="1">
         <v>1</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O7" s="1">
         <v>0</v>
@@ -2838,10 +2859,10 @@
         <v>0</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y7" s="1">
         <v>0</v>
@@ -2904,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="AS7" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT7" s="1">
         <v>0</v>
@@ -2925,7 +2946,7 @@
         <v>0</v>
       </c>
       <c r="AZ7" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA7" s="1">
         <v>0</v>
@@ -2937,7 +2958,7 @@
         <v>0</v>
       </c>
       <c r="BD7" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE7" s="1">
         <v>0</v>
@@ -2957,13 +2978,13 @@
         <v>5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -2971,23 +2992,23 @@
       <c r="H8" s="1">
         <v>0</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K8" s="1">
         <v>1</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O8" s="1">
         <v>0</v>
@@ -3014,10 +3035,10 @@
         <v>0</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X8" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y8" s="1">
         <v>0</v>
@@ -3080,7 +3101,7 @@
         <v>0</v>
       </c>
       <c r="AS8" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT8" s="1">
         <v>0</v>
@@ -3101,7 +3122,7 @@
         <v>0</v>
       </c>
       <c r="AZ8" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA8" s="1">
         <v>0</v>
@@ -3113,7 +3134,7 @@
         <v>0</v>
       </c>
       <c r="BD8" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE8" s="1">
         <v>0</v>
@@ -3133,13 +3154,13 @@
         <v>6</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
@@ -3147,23 +3168,23 @@
       <c r="H9" s="1">
         <v>0</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K9" s="1">
         <v>1</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O9" s="1">
         <v>0</v>
@@ -3190,10 +3211,10 @@
         <v>0</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X9" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y9" s="1">
         <v>0</v>
@@ -3256,7 +3277,7 @@
         <v>0</v>
       </c>
       <c r="AS9" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT9" s="1">
         <v>0</v>
@@ -3277,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="AZ9" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA9" s="1">
         <v>0</v>
@@ -3289,7 +3310,7 @@
         <v>0</v>
       </c>
       <c r="BD9" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE9" s="1">
         <v>0</v>
@@ -3309,13 +3330,13 @@
         <v>7</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G10" s="1">
         <v>1</v>
@@ -3323,23 +3344,23 @@
       <c r="H10" s="1">
         <v>0</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K10" s="1">
         <v>1</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O10" s="1">
         <v>0</v>
@@ -3366,10 +3387,10 @@
         <v>0</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X10" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y10" s="1">
         <v>0</v>
@@ -3432,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="AS10" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT10" s="1">
         <v>0</v>
@@ -3453,7 +3474,7 @@
         <v>0</v>
       </c>
       <c r="AZ10" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA10" s="1">
         <v>0</v>
@@ -3465,7 +3486,7 @@
         <v>0</v>
       </c>
       <c r="BD10" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE10" s="1">
         <v>0</v>
@@ -3485,13 +3506,13 @@
         <v>8</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G11" s="1">
         <v>1</v>
@@ -3499,23 +3520,23 @@
       <c r="H11" s="1">
         <v>0</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="J11" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K11" s="1">
         <v>1</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O11" s="1">
         <v>0</v>
@@ -3542,10 +3563,10 @@
         <v>0</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X11" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y11" s="1">
         <v>0</v>
@@ -3608,7 +3629,7 @@
         <v>0</v>
       </c>
       <c r="AS11" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT11" s="1">
         <v>0</v>
@@ -3629,7 +3650,7 @@
         <v>0</v>
       </c>
       <c r="AZ11" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA11" s="1">
         <v>0</v>
@@ -3641,7 +3662,7 @@
         <v>0</v>
       </c>
       <c r="BD11" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE11" s="1">
         <v>0</v>
@@ -3661,13 +3682,13 @@
         <v>9</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G12" s="1">
         <v>1</v>
@@ -3676,22 +3697,22 @@
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J12" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K12" s="1">
         <v>1</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O12" s="1">
         <v>0</v>
@@ -3718,10 +3739,10 @@
         <v>0</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X12" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y12" s="1">
         <v>0</v>
@@ -3784,7 +3805,7 @@
         <v>0</v>
       </c>
       <c r="AS12" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT12" s="1">
         <v>0</v>
@@ -3805,7 +3826,7 @@
         <v>0</v>
       </c>
       <c r="AZ12" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA12" s="1">
         <v>0</v>
@@ -3817,7 +3838,7 @@
         <v>0</v>
       </c>
       <c r="BD12" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE12" s="1">
         <v>0</v>
@@ -3837,13 +3858,13 @@
         <v>10</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -3852,22 +3873,22 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J13" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J13" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K13" s="1">
         <v>1</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O13" s="1">
         <v>0</v>
@@ -3894,10 +3915,10 @@
         <v>0</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X13" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y13" s="1">
         <v>0</v>
@@ -3960,7 +3981,7 @@
         <v>0</v>
       </c>
       <c r="AS13" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT13" s="1">
         <v>0</v>
@@ -3981,7 +4002,7 @@
         <v>0</v>
       </c>
       <c r="AZ13" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA13" s="1">
         <v>0</v>
@@ -3993,7 +4014,7 @@
         <v>0</v>
       </c>
       <c r="BD13" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE13" s="1">
         <v>0</v>
@@ -4013,13 +4034,13 @@
         <v>11</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -4028,22 +4049,22 @@
         <v>0</v>
       </c>
       <c r="I14" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J14" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J14" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K14" s="1">
         <v>1</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O14" s="1">
         <v>0</v>
@@ -4070,10 +4091,10 @@
         <v>0</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y14" s="1">
         <v>0</v>
@@ -4136,7 +4157,7 @@
         <v>0</v>
       </c>
       <c r="AS14" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT14" s="1">
         <v>0</v>
@@ -4157,7 +4178,7 @@
         <v>0</v>
       </c>
       <c r="AZ14" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA14" s="1">
         <v>0</v>
@@ -4169,7 +4190,7 @@
         <v>0</v>
       </c>
       <c r="BD14" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE14" s="1">
         <v>0</v>
@@ -4189,13 +4210,13 @@
         <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G15" s="1">
         <v>1</v>
@@ -4204,22 +4225,22 @@
         <v>0</v>
       </c>
       <c r="I15" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J15" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K15" s="1">
         <v>1</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O15" s="1">
         <v>0</v>
@@ -4246,10 +4267,10 @@
         <v>0</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X15" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y15" s="1">
         <v>0</v>
@@ -4312,7 +4333,7 @@
         <v>0</v>
       </c>
       <c r="AS15" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT15" s="1">
         <v>0</v>
@@ -4333,7 +4354,7 @@
         <v>0</v>
       </c>
       <c r="AZ15" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA15" s="1">
         <v>0</v>
@@ -4345,7 +4366,7 @@
         <v>0</v>
       </c>
       <c r="BD15" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE15" s="1">
         <v>0</v>
@@ -4365,13 +4386,13 @@
         <v>13</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G16" s="1">
         <v>1</v>
@@ -4380,22 +4401,22 @@
         <v>0</v>
       </c>
       <c r="I16" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J16" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J16" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K16" s="1">
         <v>1</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O16" s="1">
         <v>0</v>
@@ -4422,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X16" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y16" s="1">
         <v>0</v>
@@ -4488,7 +4509,7 @@
         <v>0</v>
       </c>
       <c r="AS16" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT16" s="1">
         <v>0</v>
@@ -4509,7 +4530,7 @@
         <v>0</v>
       </c>
       <c r="AZ16" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA16" s="1">
         <v>0</v>
@@ -4521,7 +4542,7 @@
         <v>0</v>
       </c>
       <c r="BD16" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE16" s="1">
         <v>0</v>
@@ -4541,13 +4562,13 @@
         <v>14</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G17" s="1">
         <v>1</v>
@@ -4556,22 +4577,22 @@
         <v>0</v>
       </c>
       <c r="I17" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J17" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K17" s="1">
         <v>1</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O17" s="1">
         <v>0</v>
@@ -4598,10 +4619,10 @@
         <v>0</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X17" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y17" s="1">
         <v>0</v>
@@ -4664,7 +4685,7 @@
         <v>0</v>
       </c>
       <c r="AS17" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT17" s="1">
         <v>0</v>
@@ -4685,7 +4706,7 @@
         <v>0</v>
       </c>
       <c r="AZ17" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA17" s="1">
         <v>0</v>
@@ -4697,7 +4718,7 @@
         <v>0</v>
       </c>
       <c r="BD17" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE17" s="1">
         <v>0</v>
@@ -4717,13 +4738,13 @@
         <v>15</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G18" s="1">
         <v>1</v>
@@ -4732,22 +4753,22 @@
         <v>0</v>
       </c>
       <c r="I18" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J18" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K18" s="1">
         <v>1</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O18" s="1">
         <v>0</v>
@@ -4774,10 +4795,10 @@
         <v>0</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X18" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y18" s="1">
         <v>0</v>
@@ -4840,7 +4861,7 @@
         <v>0</v>
       </c>
       <c r="AS18" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT18" s="1">
         <v>0</v>
@@ -4861,7 +4882,7 @@
         <v>0</v>
       </c>
       <c r="AZ18" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA18" s="1">
         <v>0</v>
@@ -4873,7 +4894,7 @@
         <v>0</v>
       </c>
       <c r="BD18" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE18" s="1">
         <v>0</v>
@@ -4893,13 +4914,13 @@
         <v>16</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G19" s="1">
         <v>1</v>
@@ -4908,22 +4929,22 @@
         <v>0</v>
       </c>
       <c r="I19" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J19" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K19" s="1">
         <v>1</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O19" s="1">
         <v>0</v>
@@ -4950,10 +4971,10 @@
         <v>0</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X19" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y19" s="1">
         <v>0</v>
@@ -5016,7 +5037,7 @@
         <v>0</v>
       </c>
       <c r="AS19" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT19" s="1">
         <v>0</v>
@@ -5037,7 +5058,7 @@
         <v>0</v>
       </c>
       <c r="AZ19" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA19" s="1">
         <v>0</v>
@@ -5049,7 +5070,7 @@
         <v>0</v>
       </c>
       <c r="BD19" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE19" s="1">
         <v>0</v>
@@ -5069,13 +5090,13 @@
         <v>17</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G20" s="1">
         <v>1</v>
@@ -5084,22 +5105,22 @@
         <v>0</v>
       </c>
       <c r="I20" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J20" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J20" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K20" s="1">
         <v>1</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O20" s="1">
         <v>0</v>
@@ -5126,10 +5147,10 @@
         <v>0</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X20" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y20" s="1">
         <v>0</v>
@@ -5192,7 +5213,7 @@
         <v>0</v>
       </c>
       <c r="AS20" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT20" s="1">
         <v>0</v>
@@ -5213,7 +5234,7 @@
         <v>0</v>
       </c>
       <c r="AZ20" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA20" s="1">
         <v>0</v>
@@ -5225,7 +5246,7 @@
         <v>0</v>
       </c>
       <c r="BD20" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE20" s="1">
         <v>0</v>
@@ -5245,13 +5266,13 @@
         <v>18</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G21" s="1">
         <v>1</v>
@@ -5260,22 +5281,22 @@
         <v>0</v>
       </c>
       <c r="I21" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J21" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J21" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K21" s="1">
         <v>1</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O21" s="1">
         <v>0</v>
@@ -5302,10 +5323,10 @@
         <v>0</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X21" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y21" s="1">
         <v>0</v>
@@ -5368,7 +5389,7 @@
         <v>0</v>
       </c>
       <c r="AS21" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT21" s="1">
         <v>0</v>
@@ -5389,7 +5410,7 @@
         <v>0</v>
       </c>
       <c r="AZ21" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA21" s="1">
         <v>0</v>
@@ -5401,7 +5422,7 @@
         <v>0</v>
       </c>
       <c r="BD21" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE21" s="1">
         <v>0</v>
@@ -5421,13 +5442,13 @@
         <v>19</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G22" s="1">
         <v>1</v>
@@ -5436,22 +5457,22 @@
         <v>0</v>
       </c>
       <c r="I22" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J22" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J22" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K22" s="1">
         <v>1</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O22" s="1">
         <v>0</v>
@@ -5478,10 +5499,10 @@
         <v>0</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X22" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y22" s="1">
         <v>0</v>
@@ -5544,7 +5565,7 @@
         <v>0</v>
       </c>
       <c r="AS22" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT22" s="1">
         <v>0</v>
@@ -5565,7 +5586,7 @@
         <v>0</v>
       </c>
       <c r="AZ22" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA22" s="1">
         <v>0</v>
@@ -5577,7 +5598,7 @@
         <v>0</v>
       </c>
       <c r="BD22" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE22" s="1">
         <v>0</v>
@@ -5597,13 +5618,13 @@
         <v>20</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G23" s="1">
         <v>1</v>
@@ -5612,22 +5633,22 @@
         <v>0</v>
       </c>
       <c r="I23" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J23" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J23" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K23" s="1">
         <v>1</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O23" s="1">
         <v>0</v>
@@ -5654,10 +5675,10 @@
         <v>0</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X23" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y23" s="1">
         <v>0</v>
@@ -5720,7 +5741,7 @@
         <v>0</v>
       </c>
       <c r="AS23" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT23" s="1">
         <v>0</v>
@@ -5741,7 +5762,7 @@
         <v>0</v>
       </c>
       <c r="AZ23" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA23" s="1">
         <v>0</v>
@@ -5753,7 +5774,7 @@
         <v>0</v>
       </c>
       <c r="BD23" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE23" s="1">
         <v>0</v>
@@ -5773,13 +5794,13 @@
         <v>21</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G24" s="1">
         <v>1</v>
@@ -5788,22 +5809,22 @@
         <v>0</v>
       </c>
       <c r="I24" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J24" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J24" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K24" s="1">
         <v>1</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O24" s="1">
         <v>0</v>
@@ -5830,10 +5851,10 @@
         <v>0</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X24" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y24" s="1">
         <v>0</v>
@@ -5896,7 +5917,7 @@
         <v>0</v>
       </c>
       <c r="AS24" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT24" s="1">
         <v>0</v>
@@ -5917,7 +5938,7 @@
         <v>0</v>
       </c>
       <c r="AZ24" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA24" s="1">
         <v>0</v>
@@ -5929,7 +5950,7 @@
         <v>0</v>
       </c>
       <c r="BD24" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE24" s="1">
         <v>0</v>
@@ -5949,13 +5970,13 @@
         <v>22</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G25" s="1">
         <v>1</v>
@@ -5964,22 +5985,22 @@
         <v>0</v>
       </c>
       <c r="I25" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J25" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J25" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K25" s="1">
         <v>1</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O25" s="1">
         <v>0</v>
@@ -6006,10 +6027,10 @@
         <v>0</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X25" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y25" s="1">
         <v>0</v>
@@ -6072,7 +6093,7 @@
         <v>0</v>
       </c>
       <c r="AS25" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT25" s="1">
         <v>0</v>
@@ -6093,7 +6114,7 @@
         <v>0</v>
       </c>
       <c r="AZ25" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA25" s="1">
         <v>0</v>
@@ -6105,7 +6126,7 @@
         <v>0</v>
       </c>
       <c r="BD25" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE25" s="1">
         <v>0</v>
@@ -6125,13 +6146,13 @@
         <v>23</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G26" s="1">
         <v>1</v>
@@ -6140,22 +6161,22 @@
         <v>0</v>
       </c>
       <c r="I26" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J26" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J26" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K26" s="1">
         <v>1</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O26" s="1">
         <v>0</v>
@@ -6182,10 +6203,10 @@
         <v>0</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X26" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y26" s="1">
         <v>0</v>
@@ -6248,7 +6269,7 @@
         <v>0</v>
       </c>
       <c r="AS26" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT26" s="1">
         <v>0</v>
@@ -6269,7 +6290,7 @@
         <v>0</v>
       </c>
       <c r="AZ26" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA26" s="1">
         <v>0</v>
@@ -6281,7 +6302,7 @@
         <v>0</v>
       </c>
       <c r="BD26" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE26" s="1">
         <v>0</v>
@@ -6301,13 +6322,13 @@
         <v>24</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G27" s="1">
         <v>1</v>
@@ -6316,22 +6337,22 @@
         <v>0</v>
       </c>
       <c r="I27" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J27" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J27" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K27" s="1">
         <v>1</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O27" s="1">
         <v>0</v>
@@ -6358,10 +6379,10 @@
         <v>0</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X27" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y27" s="1">
         <v>0</v>
@@ -6424,7 +6445,7 @@
         <v>0</v>
       </c>
       <c r="AS27" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT27" s="1">
         <v>0</v>
@@ -6445,7 +6466,7 @@
         <v>0</v>
       </c>
       <c r="AZ27" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA27" s="1">
         <v>0</v>
@@ -6457,7 +6478,7 @@
         <v>0</v>
       </c>
       <c r="BD27" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE27" s="1">
         <v>0</v>
@@ -6477,13 +6498,13 @@
         <v>25</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G28" s="1">
         <v>1</v>
@@ -6492,22 +6513,22 @@
         <v>0</v>
       </c>
       <c r="I28" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J28" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J28" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K28" s="1">
         <v>1</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O28" s="1">
         <v>0</v>
@@ -6534,10 +6555,10 @@
         <v>0</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X28" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y28" s="1">
         <v>0</v>
@@ -6600,7 +6621,7 @@
         <v>0</v>
       </c>
       <c r="AS28" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT28" s="1">
         <v>0</v>
@@ -6621,7 +6642,7 @@
         <v>0</v>
       </c>
       <c r="AZ28" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA28" s="1">
         <v>0</v>
@@ -6633,7 +6654,7 @@
         <v>0</v>
       </c>
       <c r="BD28" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE28" s="1">
         <v>0</v>
@@ -6653,13 +6674,13 @@
         <v>26</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G29" s="1">
         <v>1</v>
@@ -6668,22 +6689,22 @@
         <v>0</v>
       </c>
       <c r="I29" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J29" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J29" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K29" s="1">
         <v>1</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O29" s="1">
         <v>0</v>
@@ -6710,10 +6731,10 @@
         <v>0</v>
       </c>
       <c r="W29" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X29" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y29" s="1">
         <v>0</v>
@@ -6776,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="AS29" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT29" s="1">
         <v>0</v>
@@ -6797,7 +6818,7 @@
         <v>0</v>
       </c>
       <c r="AZ29" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA29" s="1">
         <v>0</v>
@@ -6809,7 +6830,7 @@
         <v>0</v>
       </c>
       <c r="BD29" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE29" s="1">
         <v>0</v>
@@ -6829,13 +6850,13 @@
         <v>27</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G30" s="1">
         <v>1</v>
@@ -6844,22 +6865,22 @@
         <v>0</v>
       </c>
       <c r="I30" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J30" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J30" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K30" s="1">
         <v>1</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O30" s="1">
         <v>0</v>
@@ -6886,10 +6907,10 @@
         <v>0</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X30" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y30" s="1">
         <v>0</v>
@@ -6952,7 +6973,7 @@
         <v>0</v>
       </c>
       <c r="AS30" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT30" s="1">
         <v>0</v>
@@ -6973,7 +6994,7 @@
         <v>0</v>
       </c>
       <c r="AZ30" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA30" s="1">
         <v>0</v>
@@ -6985,7 +7006,7 @@
         <v>0</v>
       </c>
       <c r="BD30" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE30" s="1">
         <v>0</v>
@@ -7005,13 +7026,13 @@
         <v>28</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -7020,22 +7041,22 @@
         <v>0</v>
       </c>
       <c r="I31" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J31" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J31" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K31" s="1">
         <v>1</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O31" s="1">
         <v>0</v>
@@ -7062,10 +7083,10 @@
         <v>0</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X31" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y31" s="1">
         <v>0</v>
@@ -7128,7 +7149,7 @@
         <v>0</v>
       </c>
       <c r="AS31" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT31" s="1">
         <v>0</v>
@@ -7149,7 +7170,7 @@
         <v>0</v>
       </c>
       <c r="AZ31" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA31" s="1">
         <v>0</v>
@@ -7161,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="BD31" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE31" s="1">
         <v>0</v>
@@ -7181,13 +7202,13 @@
         <v>29</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G32" s="1">
         <v>1</v>
@@ -7196,22 +7217,22 @@
         <v>0</v>
       </c>
       <c r="I32" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J32" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J32" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K32" s="1">
         <v>1</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O32" s="1">
         <v>0</v>
@@ -7238,10 +7259,10 @@
         <v>0</v>
       </c>
       <c r="W32" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X32" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y32" s="1">
         <v>0</v>
@@ -7304,7 +7325,7 @@
         <v>0</v>
       </c>
       <c r="AS32" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT32" s="1">
         <v>0</v>
@@ -7325,7 +7346,7 @@
         <v>0</v>
       </c>
       <c r="AZ32" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA32" s="1">
         <v>0</v>
@@ -7337,7 +7358,7 @@
         <v>0</v>
       </c>
       <c r="BD32" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE32" s="1">
         <v>0</v>
@@ -7357,13 +7378,13 @@
         <v>30</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G33" s="1">
         <v>1</v>
@@ -7372,22 +7393,22 @@
         <v>0</v>
       </c>
       <c r="I33" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J33" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J33" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K33" s="1">
         <v>1</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O33" s="1">
         <v>0</v>
@@ -7414,10 +7435,10 @@
         <v>0</v>
       </c>
       <c r="W33" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X33" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y33" s="1">
         <v>0</v>
@@ -7480,7 +7501,7 @@
         <v>0</v>
       </c>
       <c r="AS33" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT33" s="1">
         <v>0</v>
@@ -7501,7 +7522,7 @@
         <v>0</v>
       </c>
       <c r="AZ33" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA33" s="1">
         <v>0</v>
@@ -7513,7 +7534,7 @@
         <v>0</v>
       </c>
       <c r="BD33" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE33" s="1">
         <v>0</v>
@@ -7533,13 +7554,13 @@
         <v>1</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G34" s="1">
         <v>1</v>
@@ -7548,22 +7569,22 @@
         <v>0</v>
       </c>
       <c r="I34" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J34" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J34" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K34" s="1">
         <v>1</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O34" s="1">
         <v>0</v>
@@ -7590,10 +7611,10 @@
         <v>0</v>
       </c>
       <c r="W34" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X34" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y34" s="1">
         <v>0</v>
@@ -7656,7 +7677,7 @@
         <v>0</v>
       </c>
       <c r="AS34" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT34" s="1">
         <v>0</v>
@@ -7677,7 +7698,7 @@
         <v>0</v>
       </c>
       <c r="AZ34" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA34" s="1">
         <v>0</v>
@@ -7689,7 +7710,7 @@
         <v>0</v>
       </c>
       <c r="BD34" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE34" s="1">
         <v>0</v>
@@ -7709,13 +7730,13 @@
         <v>2</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G35" s="1">
         <v>1</v>
@@ -7724,22 +7745,22 @@
         <v>0</v>
       </c>
       <c r="I35" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J35" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J35" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K35" s="1">
         <v>1</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O35" s="1">
         <v>0</v>
@@ -7766,10 +7787,10 @@
         <v>0</v>
       </c>
       <c r="W35" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X35" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y35" s="1">
         <v>0</v>
@@ -7832,7 +7853,7 @@
         <v>0</v>
       </c>
       <c r="AS35" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT35" s="1">
         <v>0</v>
@@ -7853,7 +7874,7 @@
         <v>0</v>
       </c>
       <c r="AZ35" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA35" s="1">
         <v>0</v>
@@ -7865,7 +7886,7 @@
         <v>0</v>
       </c>
       <c r="BD35" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE35" s="1">
         <v>0</v>
@@ -7885,13 +7906,13 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G36" s="1">
         <v>1</v>
@@ -7900,22 +7921,22 @@
         <v>0</v>
       </c>
       <c r="I36" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J36" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J36" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K36" s="1">
         <v>1</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O36" s="1">
         <v>0</v>
@@ -7942,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="W36" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X36" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y36" s="1">
         <v>0</v>
@@ -8008,7 +8029,7 @@
         <v>0</v>
       </c>
       <c r="AS36" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT36" s="1">
         <v>0</v>
@@ -8029,7 +8050,7 @@
         <v>0</v>
       </c>
       <c r="AZ36" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA36" s="1">
         <v>0</v>
@@ -8041,7 +8062,7 @@
         <v>0</v>
       </c>
       <c r="BD36" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE36" s="1">
         <v>0</v>
@@ -8061,13 +8082,13 @@
         <v>4</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G37" s="1">
         <v>1</v>
@@ -8076,22 +8097,22 @@
         <v>0</v>
       </c>
       <c r="I37" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J37" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J37" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K37" s="1">
         <v>1</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O37" s="1">
         <v>0</v>
@@ -8118,10 +8139,10 @@
         <v>0</v>
       </c>
       <c r="W37" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X37" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y37" s="1">
         <v>0</v>
@@ -8184,7 +8205,7 @@
         <v>0</v>
       </c>
       <c r="AS37" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT37" s="1">
         <v>0</v>
@@ -8205,7 +8226,7 @@
         <v>0</v>
       </c>
       <c r="AZ37" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA37" s="1">
         <v>0</v>
@@ -8217,7 +8238,7 @@
         <v>0</v>
       </c>
       <c r="BD37" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE37" s="1">
         <v>0</v>
@@ -8237,13 +8258,13 @@
         <v>5</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G38" s="1">
         <v>1</v>
@@ -8252,22 +8273,22 @@
         <v>0</v>
       </c>
       <c r="I38" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J38" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J38" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K38" s="1">
         <v>1</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O38" s="1">
         <v>0</v>
@@ -8294,10 +8315,10 @@
         <v>0</v>
       </c>
       <c r="W38" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X38" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y38" s="1">
         <v>0</v>
@@ -8360,7 +8381,7 @@
         <v>0</v>
       </c>
       <c r="AS38" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT38" s="1">
         <v>0</v>
@@ -8381,7 +8402,7 @@
         <v>0</v>
       </c>
       <c r="AZ38" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA38" s="1">
         <v>0</v>
@@ -8393,7 +8414,7 @@
         <v>0</v>
       </c>
       <c r="BD38" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE38" s="1">
         <v>0</v>
@@ -8413,13 +8434,13 @@
         <v>6</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G39" s="1">
         <v>1</v>
@@ -8428,22 +8449,22 @@
         <v>0</v>
       </c>
       <c r="I39" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J39" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J39" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K39" s="1">
         <v>1</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O39" s="1">
         <v>0</v>
@@ -8470,10 +8491,10 @@
         <v>0</v>
       </c>
       <c r="W39" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X39" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y39" s="1">
         <v>0</v>
@@ -8536,7 +8557,7 @@
         <v>0</v>
       </c>
       <c r="AS39" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT39" s="1">
         <v>0</v>
@@ -8557,7 +8578,7 @@
         <v>0</v>
       </c>
       <c r="AZ39" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA39" s="1">
         <v>0</v>
@@ -8569,7 +8590,7 @@
         <v>0</v>
       </c>
       <c r="BD39" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE39" s="1">
         <v>0</v>
@@ -8589,13 +8610,13 @@
         <v>7</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G40" s="1">
         <v>1</v>
@@ -8604,22 +8625,22 @@
         <v>0</v>
       </c>
       <c r="I40" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J40" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J40" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K40" s="1">
         <v>1</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O40" s="1">
         <v>0</v>
@@ -8646,10 +8667,10 @@
         <v>0</v>
       </c>
       <c r="W40" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X40" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y40" s="1">
         <v>0</v>
@@ -8712,7 +8733,7 @@
         <v>0</v>
       </c>
       <c r="AS40" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT40" s="1">
         <v>0</v>
@@ -8733,7 +8754,7 @@
         <v>0</v>
       </c>
       <c r="AZ40" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA40" s="1">
         <v>0</v>
@@ -8745,7 +8766,7 @@
         <v>0</v>
       </c>
       <c r="BD40" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE40" s="1">
         <v>0</v>
@@ -8765,13 +8786,13 @@
         <v>8</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G41" s="1">
         <v>1</v>
@@ -8780,22 +8801,22 @@
         <v>0</v>
       </c>
       <c r="I41" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J41" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J41" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K41" s="1">
         <v>1</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O41" s="1">
         <v>0</v>
@@ -8822,10 +8843,10 @@
         <v>0</v>
       </c>
       <c r="W41" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X41" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y41" s="1">
         <v>0</v>
@@ -8888,7 +8909,7 @@
         <v>0</v>
       </c>
       <c r="AS41" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT41" s="1">
         <v>0</v>
@@ -8909,7 +8930,7 @@
         <v>0</v>
       </c>
       <c r="AZ41" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA41" s="1">
         <v>0</v>
@@ -8921,7 +8942,7 @@
         <v>0</v>
       </c>
       <c r="BD41" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE41" s="1">
         <v>0</v>
@@ -8941,13 +8962,13 @@
         <v>9</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G42" s="1">
         <v>1</v>
@@ -8956,22 +8977,22 @@
         <v>0</v>
       </c>
       <c r="I42" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J42" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J42" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K42" s="1">
         <v>1</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O42" s="1">
         <v>0</v>
@@ -8998,10 +9019,10 @@
         <v>0</v>
       </c>
       <c r="W42" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X42" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y42" s="1">
         <v>0</v>
@@ -9064,7 +9085,7 @@
         <v>0</v>
       </c>
       <c r="AS42" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT42" s="1">
         <v>0</v>
@@ -9085,7 +9106,7 @@
         <v>0</v>
       </c>
       <c r="AZ42" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA42" s="1">
         <v>0</v>
@@ -9097,7 +9118,7 @@
         <v>0</v>
       </c>
       <c r="BD42" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE42" s="1">
         <v>0</v>
@@ -9117,13 +9138,13 @@
         <v>10</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G43" s="1">
         <v>1</v>
@@ -9132,22 +9153,22 @@
         <v>0</v>
       </c>
       <c r="I43" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J43" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J43" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K43" s="1">
         <v>1</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O43" s="1">
         <v>0</v>
@@ -9174,10 +9195,10 @@
         <v>0</v>
       </c>
       <c r="W43" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X43" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y43" s="1">
         <v>0</v>
@@ -9240,7 +9261,7 @@
         <v>0</v>
       </c>
       <c r="AS43" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT43" s="1">
         <v>0</v>
@@ -9261,7 +9282,7 @@
         <v>0</v>
       </c>
       <c r="AZ43" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA43" s="1">
         <v>0</v>
@@ -9273,7 +9294,7 @@
         <v>0</v>
       </c>
       <c r="BD43" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE43" s="1">
         <v>0</v>
@@ -9293,13 +9314,13 @@
         <v>11</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G44" s="1">
         <v>1</v>
@@ -9308,22 +9329,22 @@
         <v>0</v>
       </c>
       <c r="I44" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J44" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J44" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K44" s="1">
         <v>1</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O44" s="1">
         <v>0</v>
@@ -9350,10 +9371,10 @@
         <v>0</v>
       </c>
       <c r="W44" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X44" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y44" s="1">
         <v>0</v>
@@ -9416,7 +9437,7 @@
         <v>0</v>
       </c>
       <c r="AS44" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT44" s="1">
         <v>0</v>
@@ -9437,7 +9458,7 @@
         <v>0</v>
       </c>
       <c r="AZ44" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA44" s="1">
         <v>0</v>
@@ -9449,7 +9470,7 @@
         <v>0</v>
       </c>
       <c r="BD44" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE44" s="1">
         <v>0</v>
@@ -9469,13 +9490,13 @@
         <v>12</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G45" s="1">
         <v>1</v>
@@ -9484,22 +9505,22 @@
         <v>0</v>
       </c>
       <c r="I45" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J45" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J45" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K45" s="1">
         <v>1</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O45" s="1">
         <v>0</v>
@@ -9526,10 +9547,10 @@
         <v>0</v>
       </c>
       <c r="W45" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X45" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y45" s="1">
         <v>0</v>
@@ -9592,7 +9613,7 @@
         <v>0</v>
       </c>
       <c r="AS45" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT45" s="1">
         <v>0</v>
@@ -9613,7 +9634,7 @@
         <v>0</v>
       </c>
       <c r="AZ45" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA45" s="1">
         <v>0</v>
@@ -9625,7 +9646,7 @@
         <v>0</v>
       </c>
       <c r="BD45" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE45" s="1">
         <v>0</v>
@@ -9645,13 +9666,13 @@
         <v>13</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G46" s="1">
         <v>1</v>
@@ -9660,22 +9681,22 @@
         <v>0</v>
       </c>
       <c r="I46" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J46" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J46" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K46" s="1">
         <v>1</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O46" s="1">
         <v>0</v>
@@ -9702,10 +9723,10 @@
         <v>0</v>
       </c>
       <c r="W46" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X46" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y46" s="1">
         <v>0</v>
@@ -9768,7 +9789,7 @@
         <v>0</v>
       </c>
       <c r="AS46" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT46" s="1">
         <v>0</v>
@@ -9789,7 +9810,7 @@
         <v>0</v>
       </c>
       <c r="AZ46" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA46" s="1">
         <v>0</v>
@@ -9801,7 +9822,7 @@
         <v>0</v>
       </c>
       <c r="BD46" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE46" s="1">
         <v>0</v>
@@ -9821,13 +9842,13 @@
         <v>14</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G47" s="1">
         <v>1</v>
@@ -9836,22 +9857,22 @@
         <v>0</v>
       </c>
       <c r="I47" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J47" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J47" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K47" s="1">
         <v>1</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O47" s="1">
         <v>0</v>
@@ -9878,10 +9899,10 @@
         <v>0</v>
       </c>
       <c r="W47" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X47" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y47" s="1">
         <v>0</v>
@@ -9944,7 +9965,7 @@
         <v>0</v>
       </c>
       <c r="AS47" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT47" s="1">
         <v>0</v>
@@ -9965,7 +9986,7 @@
         <v>0</v>
       </c>
       <c r="AZ47" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA47" s="1">
         <v>0</v>
@@ -9977,7 +9998,7 @@
         <v>0</v>
       </c>
       <c r="BD47" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE47" s="1">
         <v>0</v>
@@ -9997,13 +10018,13 @@
         <v>15</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G48" s="1">
         <v>1</v>
@@ -10012,22 +10033,22 @@
         <v>0</v>
       </c>
       <c r="I48" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J48" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J48" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K48" s="1">
         <v>1</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O48" s="1">
         <v>0</v>
@@ -10054,10 +10075,10 @@
         <v>0</v>
       </c>
       <c r="W48" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X48" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y48" s="1">
         <v>0</v>
@@ -10120,7 +10141,7 @@
         <v>0</v>
       </c>
       <c r="AS48" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT48" s="1">
         <v>0</v>
@@ -10141,7 +10162,7 @@
         <v>0</v>
       </c>
       <c r="AZ48" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA48" s="1">
         <v>0</v>
@@ -10153,7 +10174,7 @@
         <v>0</v>
       </c>
       <c r="BD48" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE48" s="1">
         <v>0</v>
@@ -10173,13 +10194,13 @@
         <v>16</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G49" s="1">
         <v>1</v>
@@ -10188,22 +10209,22 @@
         <v>0</v>
       </c>
       <c r="I49" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J49" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J49" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K49" s="1">
         <v>1</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O49" s="1">
         <v>0</v>
@@ -10230,10 +10251,10 @@
         <v>0</v>
       </c>
       <c r="W49" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X49" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y49" s="1">
         <v>0</v>
@@ -10296,7 +10317,7 @@
         <v>0</v>
       </c>
       <c r="AS49" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT49" s="1">
         <v>0</v>
@@ -10317,7 +10338,7 @@
         <v>0</v>
       </c>
       <c r="AZ49" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA49" s="1">
         <v>0</v>
@@ -10329,7 +10350,7 @@
         <v>0</v>
       </c>
       <c r="BD49" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE49" s="1">
         <v>0</v>
@@ -10349,13 +10370,13 @@
         <v>17</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G50" s="1">
         <v>1</v>
@@ -10364,22 +10385,22 @@
         <v>0</v>
       </c>
       <c r="I50" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J50" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J50" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K50" s="1">
         <v>1</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O50" s="1">
         <v>0</v>
@@ -10406,10 +10427,10 @@
         <v>0</v>
       </c>
       <c r="W50" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X50" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y50" s="1">
         <v>0</v>
@@ -10472,7 +10493,7 @@
         <v>0</v>
       </c>
       <c r="AS50" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT50" s="1">
         <v>0</v>
@@ -10493,7 +10514,7 @@
         <v>0</v>
       </c>
       <c r="AZ50" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA50" s="1">
         <v>0</v>
@@ -10505,7 +10526,7 @@
         <v>0</v>
       </c>
       <c r="BD50" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE50" s="1">
         <v>0</v>
@@ -10525,13 +10546,13 @@
         <v>18</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G51" s="1">
         <v>1</v>
@@ -10540,22 +10561,22 @@
         <v>0</v>
       </c>
       <c r="I51" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J51" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J51" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K51" s="1">
         <v>1</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M51" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O51" s="1">
         <v>0</v>
@@ -10582,10 +10603,10 @@
         <v>0</v>
       </c>
       <c r="W51" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X51" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y51" s="1">
         <v>0</v>
@@ -10648,7 +10669,7 @@
         <v>0</v>
       </c>
       <c r="AS51" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT51" s="1">
         <v>0</v>
@@ -10669,7 +10690,7 @@
         <v>0</v>
       </c>
       <c r="AZ51" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA51" s="1">
         <v>0</v>
@@ -10681,7 +10702,7 @@
         <v>0</v>
       </c>
       <c r="BD51" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE51" s="1">
         <v>0</v>
@@ -10701,13 +10722,13 @@
         <v>19</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G52" s="1">
         <v>1</v>
@@ -10716,22 +10737,22 @@
         <v>0</v>
       </c>
       <c r="I52" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J52" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J52" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K52" s="1">
         <v>1</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O52" s="1">
         <v>0</v>
@@ -10758,10 +10779,10 @@
         <v>0</v>
       </c>
       <c r="W52" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X52" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y52" s="1">
         <v>0</v>
@@ -10824,7 +10845,7 @@
         <v>0</v>
       </c>
       <c r="AS52" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT52" s="1">
         <v>0</v>
@@ -10845,7 +10866,7 @@
         <v>0</v>
       </c>
       <c r="AZ52" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA52" s="1">
         <v>0</v>
@@ -10857,7 +10878,7 @@
         <v>0</v>
       </c>
       <c r="BD52" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE52" s="1">
         <v>0</v>
@@ -10877,13 +10898,13 @@
         <v>20</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G53" s="1">
         <v>1</v>
@@ -10892,22 +10913,22 @@
         <v>0</v>
       </c>
       <c r="I53" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J53" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J53" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K53" s="1">
         <v>1</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O53" s="1">
         <v>0</v>
@@ -10934,10 +10955,10 @@
         <v>0</v>
       </c>
       <c r="W53" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X53" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y53" s="1">
         <v>0</v>
@@ -11000,7 +11021,7 @@
         <v>0</v>
       </c>
       <c r="AS53" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT53" s="1">
         <v>0</v>
@@ -11021,7 +11042,7 @@
         <v>0</v>
       </c>
       <c r="AZ53" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA53" s="1">
         <v>0</v>
@@ -11033,7 +11054,7 @@
         <v>0</v>
       </c>
       <c r="BD53" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE53" s="1">
         <v>0</v>
@@ -11053,13 +11074,13 @@
         <v>21</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G54" s="1">
         <v>1</v>
@@ -11068,22 +11089,22 @@
         <v>0</v>
       </c>
       <c r="I54" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J54" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J54" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K54" s="1">
         <v>1</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O54" s="1">
         <v>0</v>
@@ -11110,10 +11131,10 @@
         <v>0</v>
       </c>
       <c r="W54" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X54" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y54" s="1">
         <v>0</v>
@@ -11176,7 +11197,7 @@
         <v>0</v>
       </c>
       <c r="AS54" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT54" s="1">
         <v>0</v>
@@ -11197,7 +11218,7 @@
         <v>0</v>
       </c>
       <c r="AZ54" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA54" s="1">
         <v>0</v>
@@ -11209,7 +11230,7 @@
         <v>0</v>
       </c>
       <c r="BD54" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE54" s="1">
         <v>0</v>
@@ -11229,13 +11250,13 @@
         <v>22</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G55" s="1">
         <v>1</v>
@@ -11244,22 +11265,22 @@
         <v>0</v>
       </c>
       <c r="I55" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J55" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J55" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K55" s="1">
         <v>1</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O55" s="1">
         <v>0</v>
@@ -11286,10 +11307,10 @@
         <v>0</v>
       </c>
       <c r="W55" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X55" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y55" s="1">
         <v>0</v>
@@ -11352,7 +11373,7 @@
         <v>0</v>
       </c>
       <c r="AS55" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT55" s="1">
         <v>0</v>
@@ -11373,7 +11394,7 @@
         <v>0</v>
       </c>
       <c r="AZ55" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA55" s="1">
         <v>0</v>
@@ -11385,7 +11406,7 @@
         <v>0</v>
       </c>
       <c r="BD55" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE55" s="1">
         <v>0</v>
@@ -11405,13 +11426,13 @@
         <v>23</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G56" s="1">
         <v>1</v>
@@ -11420,22 +11441,22 @@
         <v>0</v>
       </c>
       <c r="I56" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J56" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J56" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K56" s="1">
         <v>1</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O56" s="1">
         <v>0</v>
@@ -11462,10 +11483,10 @@
         <v>0</v>
       </c>
       <c r="W56" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X56" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y56" s="1">
         <v>0</v>
@@ -11528,7 +11549,7 @@
         <v>0</v>
       </c>
       <c r="AS56" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT56" s="1">
         <v>0</v>
@@ -11549,7 +11570,7 @@
         <v>0</v>
       </c>
       <c r="AZ56" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA56" s="1">
         <v>0</v>
@@ -11561,7 +11582,7 @@
         <v>0</v>
       </c>
       <c r="BD56" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE56" s="1">
         <v>0</v>
@@ -11581,13 +11602,13 @@
         <v>24</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G57" s="1">
         <v>1</v>
@@ -11596,22 +11617,22 @@
         <v>0</v>
       </c>
       <c r="I57" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J57" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J57" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K57" s="1">
         <v>1</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O57" s="1">
         <v>0</v>
@@ -11638,10 +11659,10 @@
         <v>0</v>
       </c>
       <c r="W57" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X57" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y57" s="1">
         <v>0</v>
@@ -11704,7 +11725,7 @@
         <v>0</v>
       </c>
       <c r="AS57" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT57" s="1">
         <v>0</v>
@@ -11725,7 +11746,7 @@
         <v>0</v>
       </c>
       <c r="AZ57" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA57" s="1">
         <v>0</v>
@@ -11737,7 +11758,7 @@
         <v>0</v>
       </c>
       <c r="BD57" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE57" s="1">
         <v>0</v>
@@ -11757,13 +11778,13 @@
         <v>25</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G58" s="1">
         <v>1</v>
@@ -11772,22 +11793,22 @@
         <v>0</v>
       </c>
       <c r="I58" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J58" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J58" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K58" s="1">
         <v>1</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O58" s="1">
         <v>0</v>
@@ -11814,10 +11835,10 @@
         <v>0</v>
       </c>
       <c r="W58" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X58" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y58" s="1">
         <v>0</v>
@@ -11880,7 +11901,7 @@
         <v>0</v>
       </c>
       <c r="AS58" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT58" s="1">
         <v>0</v>
@@ -11901,7 +11922,7 @@
         <v>0</v>
       </c>
       <c r="AZ58" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA58" s="1">
         <v>0</v>
@@ -11913,7 +11934,7 @@
         <v>0</v>
       </c>
       <c r="BD58" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE58" s="1">
         <v>0</v>
@@ -11933,13 +11954,13 @@
         <v>26</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G59" s="1">
         <v>1</v>
@@ -11948,22 +11969,22 @@
         <v>0</v>
       </c>
       <c r="I59" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J59" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J59" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K59" s="1">
         <v>1</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O59" s="1">
         <v>0</v>
@@ -11990,10 +12011,10 @@
         <v>0</v>
       </c>
       <c r="W59" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X59" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y59" s="1">
         <v>0</v>
@@ -12056,7 +12077,7 @@
         <v>0</v>
       </c>
       <c r="AS59" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT59" s="1">
         <v>0</v>
@@ -12077,7 +12098,7 @@
         <v>0</v>
       </c>
       <c r="AZ59" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA59" s="1">
         <v>0</v>
@@ -12089,7 +12110,7 @@
         <v>0</v>
       </c>
       <c r="BD59" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE59" s="1">
         <v>0</v>
@@ -12109,13 +12130,13 @@
         <v>27</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G60" s="1">
         <v>1</v>
@@ -12124,22 +12145,22 @@
         <v>0</v>
       </c>
       <c r="I60" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J60" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J60" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K60" s="1">
         <v>1</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M60" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O60" s="1">
         <v>0</v>
@@ -12166,10 +12187,10 @@
         <v>0</v>
       </c>
       <c r="W60" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X60" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y60" s="1">
         <v>0</v>
@@ -12232,7 +12253,7 @@
         <v>0</v>
       </c>
       <c r="AS60" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT60" s="1">
         <v>0</v>
@@ -12253,7 +12274,7 @@
         <v>0</v>
       </c>
       <c r="AZ60" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA60" s="1">
         <v>0</v>
@@ -12265,7 +12286,7 @@
         <v>0</v>
       </c>
       <c r="BD60" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE60" s="1">
         <v>0</v>
@@ -12285,13 +12306,13 @@
         <v>28</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G61" s="1">
         <v>1</v>
@@ -12300,22 +12321,22 @@
         <v>0</v>
       </c>
       <c r="I61" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J61" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J61" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K61" s="1">
         <v>1</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M61" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O61" s="1">
         <v>0</v>
@@ -12342,10 +12363,10 @@
         <v>0</v>
       </c>
       <c r="W61" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X61" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y61" s="1">
         <v>0</v>
@@ -12408,7 +12429,7 @@
         <v>0</v>
       </c>
       <c r="AS61" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT61" s="1">
         <v>0</v>
@@ -12429,7 +12450,7 @@
         <v>0</v>
       </c>
       <c r="AZ61" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA61" s="1">
         <v>0</v>
@@ -12441,7 +12462,7 @@
         <v>0</v>
       </c>
       <c r="BD61" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE61" s="1">
         <v>0</v>
@@ -12461,13 +12482,13 @@
         <v>29</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G62" s="1">
         <v>1</v>
@@ -12476,22 +12497,22 @@
         <v>0</v>
       </c>
       <c r="I62" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J62" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J62" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K62" s="1">
         <v>1</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M62" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O62" s="1">
         <v>0</v>
@@ -12518,10 +12539,10 @@
         <v>0</v>
       </c>
       <c r="W62" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X62" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y62" s="1">
         <v>0</v>
@@ -12584,7 +12605,7 @@
         <v>0</v>
       </c>
       <c r="AS62" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT62" s="1">
         <v>0</v>
@@ -12605,7 +12626,7 @@
         <v>0</v>
       </c>
       <c r="AZ62" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA62" s="1">
         <v>0</v>
@@ -12617,7 +12638,7 @@
         <v>0</v>
       </c>
       <c r="BD62" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE62" s="1">
         <v>0</v>
@@ -12637,13 +12658,13 @@
         <v>30</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G63" s="1">
         <v>1</v>
@@ -12652,22 +12673,22 @@
         <v>0</v>
       </c>
       <c r="I63" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J63" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J63" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K63" s="1">
         <v>1</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M63" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O63" s="1">
         <v>0</v>
@@ -12694,10 +12715,10 @@
         <v>0</v>
       </c>
       <c r="W63" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X63" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y63" s="1">
         <v>0</v>
@@ -12760,7 +12781,7 @@
         <v>0</v>
       </c>
       <c r="AS63" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT63" s="1">
         <v>0</v>
@@ -12781,7 +12802,7 @@
         <v>0</v>
       </c>
       <c r="AZ63" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA63" s="1">
         <v>0</v>
@@ -12793,7 +12814,7 @@
         <v>0</v>
       </c>
       <c r="BD63" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE63" s="1">
         <v>0</v>
@@ -12813,14 +12834,14 @@
         <v>2</v>
       </c>
       <c r="D64" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="E64" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="F64" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="E64" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="F64" s="12" t="s">
-        <v>168</v>
-      </c>
       <c r="G64" s="12">
         <v>0</v>
       </c>
@@ -12828,7 +12849,7 @@
         <v>0</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>127</v>
+        <v>192</v>
       </c>
       <c r="J64" s="4">
         <v>43400002</v>
@@ -12837,10 +12858,10 @@
         <v>5</v>
       </c>
       <c r="L64" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M64" s="12" t="s">
         <v>121</v>
-      </c>
-      <c r="M64" s="12" t="s">
-        <v>122</v>
       </c>
       <c r="N64" s="12">
         <v>0</v>
@@ -12870,10 +12891,10 @@
         <v>0</v>
       </c>
       <c r="W64" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X64" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y64" s="12">
         <v>0</v>
@@ -12936,7 +12957,7 @@
         <v>2</v>
       </c>
       <c r="AS64" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT64" s="1">
         <v>0</v>
@@ -12957,7 +12978,7 @@
         <v>0</v>
       </c>
       <c r="AZ64" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA64" s="10">
         <v>0</v>
@@ -12969,7 +12990,7 @@
         <v>0</v>
       </c>
       <c r="BD64" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE64" s="4">
         <v>43400002</v>
@@ -12989,37 +13010,37 @@
         <v>1</v>
       </c>
       <c r="D65" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F65" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="G65" s="1">
+        <v>1</v>
+      </c>
+      <c r="H65" s="1">
+        <v>0</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J65" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="F65" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="G65" s="1">
-        <v>1</v>
-      </c>
-      <c r="H65" s="1">
-        <v>0</v>
-      </c>
-      <c r="I65" s="1" t="s">
+      <c r="K65" s="1">
+        <v>1</v>
+      </c>
+      <c r="L65" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="J65" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="K65" s="1">
-        <v>1</v>
-      </c>
-      <c r="L65" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="M65" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N65" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O65" s="1">
         <v>0</v>
@@ -13046,10 +13067,10 @@
         <v>0</v>
       </c>
       <c r="W65" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X65" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y65" s="1">
         <v>0</v>
@@ -13112,7 +13133,7 @@
         <v>0</v>
       </c>
       <c r="AS65" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT65" s="1">
         <v>0</v>
@@ -13133,7 +13154,7 @@
         <v>0</v>
       </c>
       <c r="AZ65" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA65" s="1">
         <v>0</v>
@@ -13145,7 +13166,7 @@
         <v>0</v>
       </c>
       <c r="BD65" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE65" s="1">
         <v>0</v>
@@ -13165,13 +13186,13 @@
         <v>1</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G66" s="1">
         <v>1</v>
@@ -13180,7 +13201,7 @@
         <v>0</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>127</v>
+        <v>192</v>
       </c>
       <c r="J66" s="1">
         <v>44300001</v>
@@ -13189,13 +13210,13 @@
         <v>1</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O66" s="1">
         <v>0</v>
@@ -13222,10 +13243,10 @@
         <v>0</v>
       </c>
       <c r="W66" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X66" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y66" s="1">
         <v>0</v>
@@ -13288,7 +13309,7 @@
         <v>0</v>
       </c>
       <c r="AS66" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT66" s="1">
         <v>0</v>
@@ -13309,7 +13330,7 @@
         <v>0</v>
       </c>
       <c r="AZ66" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA66" s="1">
         <v>0</v>
@@ -13321,7 +13342,7 @@
         <v>0</v>
       </c>
       <c r="BD66" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE66" s="1">
         <v>0</v>
@@ -13341,13 +13362,13 @@
         <v>1</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G67" s="1">
         <v>1</v>
@@ -13356,7 +13377,7 @@
         <v>0</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>127</v>
+        <v>192</v>
       </c>
       <c r="J67" s="1">
         <v>38500001</v>
@@ -13365,13 +13386,13 @@
         <v>1</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O67" s="1">
         <v>0</v>
@@ -13398,10 +13419,10 @@
         <v>0</v>
       </c>
       <c r="W67" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X67" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y67" s="1">
         <v>0</v>
@@ -13464,7 +13485,7 @@
         <v>0</v>
       </c>
       <c r="AS67" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT67" s="1">
         <v>0</v>
@@ -13485,7 +13506,7 @@
         <v>0</v>
       </c>
       <c r="AZ67" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA67" s="1">
         <v>0</v>
@@ -13497,7 +13518,7 @@
         <v>0</v>
       </c>
       <c r="BD67" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE67" s="1">
         <v>0</v>
@@ -13517,13 +13538,13 @@
         <v>1</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G68" s="1">
         <v>0</v>
@@ -13532,7 +13553,7 @@
         <v>0</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>127</v>
+        <v>192</v>
       </c>
       <c r="J68" s="1">
         <v>45100001</v>
@@ -13541,13 +13562,13 @@
         <v>1</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M68" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O68" s="1">
         <v>0</v>
@@ -13574,10 +13595,10 @@
         <v>0</v>
       </c>
       <c r="W68" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X68" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y68" s="1">
         <v>0</v>
@@ -13640,7 +13661,7 @@
         <v>0</v>
       </c>
       <c r="AS68" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT68" s="1">
         <v>0</v>
@@ -13661,7 +13682,7 @@
         <v>0</v>
       </c>
       <c r="AZ68" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA68" s="1">
         <v>0</v>
@@ -13673,7 +13694,7 @@
         <v>0</v>
       </c>
       <c r="BD68" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE68" s="1">
         <v>0</v>
@@ -13693,13 +13714,13 @@
         <v>1</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G69" s="1">
         <v>0</v>
@@ -13708,7 +13729,7 @@
         <v>0</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>127</v>
+        <v>192</v>
       </c>
       <c r="J69" s="1">
         <v>44500001</v>
@@ -13717,13 +13738,13 @@
         <v>1</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M69" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O69" s="1">
         <v>0</v>
@@ -13750,10 +13771,10 @@
         <v>0</v>
       </c>
       <c r="W69" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X69" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y69" s="1">
         <v>0</v>
@@ -13816,7 +13837,7 @@
         <v>0</v>
       </c>
       <c r="AS69" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT69" s="1">
         <v>0</v>
@@ -13837,7 +13858,7 @@
         <v>0</v>
       </c>
       <c r="AZ69" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA69" s="1">
         <v>0</v>
@@ -13849,7 +13870,7 @@
         <v>0</v>
       </c>
       <c r="BD69" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE69" s="1">
         <v>0</v>
@@ -13869,13 +13890,13 @@
         <v>1</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G70" s="1">
         <v>0</v>
@@ -13884,22 +13905,22 @@
         <v>0</v>
       </c>
       <c r="I70" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="K70" s="1">
+        <v>1</v>
+      </c>
+      <c r="L70" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="J70" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="K70" s="1">
-        <v>1</v>
-      </c>
-      <c r="L70" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="M70" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O70" s="1">
         <v>0</v>
@@ -13926,10 +13947,10 @@
         <v>0</v>
       </c>
       <c r="W70" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X70" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y70" s="1">
         <v>0</v>
@@ -13992,7 +14013,7 @@
         <v>0</v>
       </c>
       <c r="AS70" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT70" s="1">
         <v>0</v>
@@ -14013,7 +14034,7 @@
         <v>0</v>
       </c>
       <c r="AZ70" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA70" s="1">
         <v>0</v>
@@ -14025,7 +14046,7 @@
         <v>0</v>
       </c>
       <c r="BD70" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE70" s="1">
         <v>0</v>
@@ -14045,13 +14066,13 @@
         <v>1</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G71" s="1">
         <v>0</v>
@@ -14060,7 +14081,7 @@
         <v>0</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>127</v>
+        <v>192</v>
       </c>
       <c r="J71" s="1">
         <v>45600001</v>
@@ -14069,13 +14090,13 @@
         <v>1</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M71" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O71" s="1">
         <v>0</v>
@@ -14102,10 +14123,10 @@
         <v>0</v>
       </c>
       <c r="W71" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X71" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y71" s="1">
         <v>0</v>
@@ -14168,7 +14189,7 @@
         <v>0</v>
       </c>
       <c r="AS71" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT71" s="1">
         <v>0</v>
@@ -14189,7 +14210,7 @@
         <v>0</v>
       </c>
       <c r="AZ71" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA71" s="1">
         <v>0</v>
@@ -14201,7 +14222,7 @@
         <v>0</v>
       </c>
       <c r="BD71" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE71" s="1">
         <v>0</v>
@@ -14221,13 +14242,13 @@
         <v>1</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G72" s="1">
         <v>1</v>
@@ -14236,7 +14257,7 @@
         <v>0</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>127</v>
+        <v>192</v>
       </c>
       <c r="J72" s="1">
         <v>44400001</v>
@@ -14245,13 +14266,13 @@
         <v>1</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M72" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O72" s="1">
         <v>0</v>
@@ -14278,10 +14299,10 @@
         <v>0</v>
       </c>
       <c r="W72" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X72" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y72" s="1">
         <v>0</v>
@@ -14344,7 +14365,7 @@
         <v>0</v>
       </c>
       <c r="AS72" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT72" s="1">
         <v>0</v>
@@ -14365,24 +14386,1256 @@
         <v>0</v>
       </c>
       <c r="AZ72" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA72" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB72" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC72" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD72" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE72" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF72" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:58" x14ac:dyDescent="0.15">
+      <c r="A73" s="1">
+        <v>48200001</v>
+      </c>
+      <c r="B73" s="1">
+        <v>482</v>
+      </c>
+      <c r="C73" s="1">
+        <v>1</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E73" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="F73" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="G73" s="12">
+        <v>0</v>
+      </c>
+      <c r="H73" s="12">
+        <v>0</v>
+      </c>
+      <c r="I73" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="J73" s="4">
+        <v>48200001</v>
+      </c>
+      <c r="K73" s="12">
+        <v>5</v>
+      </c>
+      <c r="L73" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M73" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="N73" s="12">
+        <v>0</v>
+      </c>
+      <c r="O73" s="12">
+        <v>0</v>
+      </c>
+      <c r="P73" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="12">
+        <v>0</v>
+      </c>
+      <c r="R73" s="12">
+        <v>0</v>
+      </c>
+      <c r="S73" s="12">
+        <v>0</v>
+      </c>
+      <c r="T73" s="12">
+        <v>3</v>
+      </c>
+      <c r="U73" s="12">
+        <v>3</v>
+      </c>
+      <c r="V73" s="12">
+        <v>0</v>
+      </c>
+      <c r="W73" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="X73" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y73" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB73" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD73" s="12">
+        <v>2</v>
+      </c>
+      <c r="AE73" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF73" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AL73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR73" s="1">
+        <v>2</v>
+      </c>
+      <c r="AS73" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="BA72" s="1">
-        <v>0</v>
-      </c>
-      <c r="BB72" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC72" s="1">
-        <v>0</v>
-      </c>
-      <c r="BD72" s="1" t="s">
+      <c r="AT73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU73" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV73" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW73" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX73" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY73" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ73" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA73" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB73" s="4">
+        <v>0</v>
+      </c>
+      <c r="BC73" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD73" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE73" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF73" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:58" x14ac:dyDescent="0.15">
+      <c r="A74" s="1">
+        <v>48300001</v>
+      </c>
+      <c r="B74" s="1">
+        <v>483</v>
+      </c>
+      <c r="C74" s="1">
+        <v>1</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="E74" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="F74" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="G74" s="12">
+        <v>0</v>
+      </c>
+      <c r="H74" s="12">
+        <v>0</v>
+      </c>
+      <c r="I74" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="J74" s="4">
+        <v>48300001</v>
+      </c>
+      <c r="K74" s="12">
+        <v>5</v>
+      </c>
+      <c r="L74" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M74" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="N74" s="12">
+        <v>0</v>
+      </c>
+      <c r="O74" s="12">
+        <v>0</v>
+      </c>
+      <c r="P74" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="12">
+        <v>0</v>
+      </c>
+      <c r="R74" s="12">
+        <v>0</v>
+      </c>
+      <c r="S74" s="12">
+        <v>0</v>
+      </c>
+      <c r="T74" s="12">
+        <v>3</v>
+      </c>
+      <c r="U74" s="12">
+        <v>3</v>
+      </c>
+      <c r="V74" s="12">
+        <v>0</v>
+      </c>
+      <c r="W74" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="X74" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y74" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB74" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD74" s="12">
+        <v>2</v>
+      </c>
+      <c r="AE74" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF74" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK74" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AL74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR74" s="1">
+        <v>2</v>
+      </c>
+      <c r="AS74" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="BE72" s="1">
-        <v>0</v>
-      </c>
-      <c r="BF72" s="1">
+      <c r="AT74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU74" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV74" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW74" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX74" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY74" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ74" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA74" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB74" s="4">
+        <v>0</v>
+      </c>
+      <c r="BC74" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD74" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE74" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF74" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:58" x14ac:dyDescent="0.15">
+      <c r="A75" s="1">
+        <v>48300002</v>
+      </c>
+      <c r="B75" s="1">
+        <v>483</v>
+      </c>
+      <c r="C75" s="1">
+        <v>2</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E75" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="F75" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="G75" s="12">
+        <v>0</v>
+      </c>
+      <c r="H75" s="12">
+        <v>0</v>
+      </c>
+      <c r="I75" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="J75" s="4">
+        <v>48300002</v>
+      </c>
+      <c r="K75" s="12">
+        <v>5</v>
+      </c>
+      <c r="L75" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M75" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="N75" s="12">
+        <v>0</v>
+      </c>
+      <c r="O75" s="12">
+        <v>0</v>
+      </c>
+      <c r="P75" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="12">
+        <v>0</v>
+      </c>
+      <c r="R75" s="12">
+        <v>0</v>
+      </c>
+      <c r="S75" s="12">
+        <v>0</v>
+      </c>
+      <c r="T75" s="12">
+        <v>3</v>
+      </c>
+      <c r="U75" s="12">
+        <v>3</v>
+      </c>
+      <c r="V75" s="12">
+        <v>0</v>
+      </c>
+      <c r="W75" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="X75" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y75" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD75" s="12">
+        <v>2</v>
+      </c>
+      <c r="AE75" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF75" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AL75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR75" s="1">
+        <v>2</v>
+      </c>
+      <c r="AS75" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="AT75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU75" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV75" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW75" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX75" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY75" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ75" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA75" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB75" s="4">
+        <v>0</v>
+      </c>
+      <c r="BC75" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD75" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE75" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF75" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:58" x14ac:dyDescent="0.15">
+      <c r="A76" s="1">
+        <v>48300003</v>
+      </c>
+      <c r="B76" s="1">
+        <v>483</v>
+      </c>
+      <c r="C76" s="1">
+        <v>3</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E76" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="F76" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="G76" s="12">
+        <v>0</v>
+      </c>
+      <c r="H76" s="12">
+        <v>0</v>
+      </c>
+      <c r="I76" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="J76" s="4">
+        <v>48300003</v>
+      </c>
+      <c r="K76" s="12">
+        <v>5</v>
+      </c>
+      <c r="L76" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M76" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="N76" s="12">
+        <v>0</v>
+      </c>
+      <c r="O76" s="12">
+        <v>0</v>
+      </c>
+      <c r="P76" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="12">
+        <v>0</v>
+      </c>
+      <c r="R76" s="12">
+        <v>0</v>
+      </c>
+      <c r="S76" s="12">
+        <v>0</v>
+      </c>
+      <c r="T76" s="12">
+        <v>3</v>
+      </c>
+      <c r="U76" s="12">
+        <v>3</v>
+      </c>
+      <c r="V76" s="12">
+        <v>0</v>
+      </c>
+      <c r="W76" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="X76" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y76" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB76" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC76" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD76" s="12">
+        <v>2</v>
+      </c>
+      <c r="AE76" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF76" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG76" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK76" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AL76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR76" s="1">
+        <v>2</v>
+      </c>
+      <c r="AS76" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="AT76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU76" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV76" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW76" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX76" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY76" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ76" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA76" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB76" s="4">
+        <v>0</v>
+      </c>
+      <c r="BC76" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD76" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE76" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF76" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:58" x14ac:dyDescent="0.15">
+      <c r="A77" s="1">
+        <v>48300004</v>
+      </c>
+      <c r="B77" s="1">
+        <v>483</v>
+      </c>
+      <c r="C77" s="1">
+        <v>4</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E77" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="F77" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="G77" s="12">
+        <v>0</v>
+      </c>
+      <c r="H77" s="12">
+        <v>0</v>
+      </c>
+      <c r="I77" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="J77" s="4">
+        <v>48300004</v>
+      </c>
+      <c r="K77" s="12">
+        <v>5</v>
+      </c>
+      <c r="L77" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M77" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="N77" s="12">
+        <v>0</v>
+      </c>
+      <c r="O77" s="12">
+        <v>0</v>
+      </c>
+      <c r="P77" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="12">
+        <v>0</v>
+      </c>
+      <c r="R77" s="12">
+        <v>0</v>
+      </c>
+      <c r="S77" s="12">
+        <v>0</v>
+      </c>
+      <c r="T77" s="12">
+        <v>3</v>
+      </c>
+      <c r="U77" s="12">
+        <v>3</v>
+      </c>
+      <c r="V77" s="12">
+        <v>0</v>
+      </c>
+      <c r="W77" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="X77" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y77" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB77" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD77" s="12">
+        <v>2</v>
+      </c>
+      <c r="AE77" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF77" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AL77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR77" s="1">
+        <v>2</v>
+      </c>
+      <c r="AS77" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="AT77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU77" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV77" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW77" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX77" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY77" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ77" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA77" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB77" s="4">
+        <v>0</v>
+      </c>
+      <c r="BC77" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD77" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE77" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF77" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:58" x14ac:dyDescent="0.15">
+      <c r="A78" s="1">
+        <v>48300005</v>
+      </c>
+      <c r="B78" s="1">
+        <v>483</v>
+      </c>
+      <c r="C78" s="1">
+        <v>5</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E78" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="F78" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="G78" s="12">
+        <v>0</v>
+      </c>
+      <c r="H78" s="12">
+        <v>0</v>
+      </c>
+      <c r="I78" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="J78" s="4">
+        <v>48300005</v>
+      </c>
+      <c r="K78" s="12">
+        <v>5</v>
+      </c>
+      <c r="L78" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M78" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="N78" s="12">
+        <v>0</v>
+      </c>
+      <c r="O78" s="12">
+        <v>0</v>
+      </c>
+      <c r="P78" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="12">
+        <v>0</v>
+      </c>
+      <c r="R78" s="12">
+        <v>0</v>
+      </c>
+      <c r="S78" s="12">
+        <v>0</v>
+      </c>
+      <c r="T78" s="12">
+        <v>3</v>
+      </c>
+      <c r="U78" s="12">
+        <v>3</v>
+      </c>
+      <c r="V78" s="12">
+        <v>0</v>
+      </c>
+      <c r="W78" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="X78" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y78" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z78" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA78" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB78" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC78" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD78" s="12">
+        <v>2</v>
+      </c>
+      <c r="AE78" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF78" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG78" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH78" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK78" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AL78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR78" s="1">
+        <v>2</v>
+      </c>
+      <c r="AS78" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="AT78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU78" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV78" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW78" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX78" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY78" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ78" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA78" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB78" s="4">
+        <v>0</v>
+      </c>
+      <c r="BC78" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD78" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE78" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF78" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:58" x14ac:dyDescent="0.15">
+      <c r="A79" s="1">
+        <v>48300006</v>
+      </c>
+      <c r="B79" s="1">
+        <v>483</v>
+      </c>
+      <c r="C79" s="1">
+        <v>6</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E79" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="F79" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="G79" s="12">
+        <v>0</v>
+      </c>
+      <c r="H79" s="12">
+        <v>0</v>
+      </c>
+      <c r="I79" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="J79" s="4">
+        <v>48300006</v>
+      </c>
+      <c r="K79" s="12">
+        <v>5</v>
+      </c>
+      <c r="L79" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M79" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="N79" s="12">
+        <v>0</v>
+      </c>
+      <c r="O79" s="12">
+        <v>0</v>
+      </c>
+      <c r="P79" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="12">
+        <v>0</v>
+      </c>
+      <c r="R79" s="12">
+        <v>0</v>
+      </c>
+      <c r="S79" s="12">
+        <v>0</v>
+      </c>
+      <c r="T79" s="12">
+        <v>3</v>
+      </c>
+      <c r="U79" s="12">
+        <v>3</v>
+      </c>
+      <c r="V79" s="12">
+        <v>0</v>
+      </c>
+      <c r="W79" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="X79" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y79" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z79" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA79" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB79" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC79" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD79" s="12">
+        <v>2</v>
+      </c>
+      <c r="AE79" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF79" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG79" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH79" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK79" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AL79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR79" s="1">
+        <v>2</v>
+      </c>
+      <c r="AS79" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="AT79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU79" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV79" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW79" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX79" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY79" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ79" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA79" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB79" s="4">
+        <v>0</v>
+      </c>
+      <c r="BC79" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD79" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE79" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF79" s="4">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18282645-7DC2-4691-A99A-DE806F821AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F690E0FE-3B5A-4843-88D2-95A9F2E12A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1128,7 +1128,7 @@
     <t>技能道具6</t>
   </si>
   <si>
-    <t>items_atlas0</t>
+    <t>items_atlas_0</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F690E0FE-3B5A-4843-88D2-95A9F2E12A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2325220-C3F9-4000-A770-CEC0DCEC2066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_items_v8" sheetId="16" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -540,7 +538,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="198">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1129,6 +1127,26 @@
   </si>
   <si>
     <t>items_atlas_0</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻速+20%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击+20%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御+20%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命上限+20%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击率+20%</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -14773,7 +14791,7 @@
         <v>187</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>165</v>
+        <v>193</v>
       </c>
       <c r="F75" s="12" t="s">
         <v>166</v>
@@ -14949,7 +14967,7 @@
         <v>188</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>165</v>
+        <v>194</v>
       </c>
       <c r="F76" s="12" t="s">
         <v>166</v>
@@ -15125,7 +15143,7 @@
         <v>189</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="F77" s="12" t="s">
         <v>166</v>
@@ -15301,7 +15319,7 @@
         <v>190</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="F78" s="12" t="s">
         <v>166</v>
@@ -15477,7 +15495,7 @@
         <v>191</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>165</v>
+        <v>197</v>
       </c>
       <c r="F79" s="12" t="s">
         <v>166</v>

--- a/servers/maze_main_server/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2325220-C3F9-4000-A770-CEC0DCEC2066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F044081-6DFA-42BF-92D3-82FA2347DC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_items_v8" sheetId="16" r:id="rId1"/>
@@ -13956,7 +13956,7 @@
         <v>0</v>
       </c>
       <c r="T70" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U70" s="1">
         <v>0</v>
@@ -14132,7 +14132,7 @@
         <v>0</v>
       </c>
       <c r="T71" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U71" s="1">
         <v>0</v>
@@ -14484,7 +14484,7 @@
         <v>0</v>
       </c>
       <c r="T73" s="12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U73" s="12">
         <v>3</v>
@@ -14660,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="T74" s="12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U74" s="12">
         <v>3</v>
@@ -14836,7 +14836,7 @@
         <v>0</v>
       </c>
       <c r="T75" s="12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U75" s="12">
         <v>3</v>
@@ -15012,7 +15012,7 @@
         <v>0</v>
       </c>
       <c r="T76" s="12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U76" s="12">
         <v>3</v>
@@ -15188,7 +15188,7 @@
         <v>0</v>
       </c>
       <c r="T77" s="12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U77" s="12">
         <v>3</v>
@@ -15364,7 +15364,7 @@
         <v>0</v>
       </c>
       <c r="T78" s="12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U78" s="12">
         <v>3</v>
@@ -15540,7 +15540,7 @@
         <v>0</v>
       </c>
       <c r="T79" s="12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U79" s="12">
         <v>3</v>

--- a/servers/maze_main_server/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F044081-6DFA-42BF-92D3-82FA2347DC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2325220-C3F9-4000-A770-CEC0DCEC2066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_items_v8" sheetId="16" r:id="rId1"/>
@@ -13956,7 +13956,7 @@
         <v>0</v>
       </c>
       <c r="T70" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U70" s="1">
         <v>0</v>
@@ -14132,7 +14132,7 @@
         <v>0</v>
       </c>
       <c r="T71" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U71" s="1">
         <v>0</v>
@@ -14484,7 +14484,7 @@
         <v>0</v>
       </c>
       <c r="T73" s="12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U73" s="12">
         <v>3</v>
@@ -14660,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="T74" s="12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U74" s="12">
         <v>3</v>
@@ -14836,7 +14836,7 @@
         <v>0</v>
       </c>
       <c r="T75" s="12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U75" s="12">
         <v>3</v>
@@ -15012,7 +15012,7 @@
         <v>0</v>
       </c>
       <c r="T76" s="12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U76" s="12">
         <v>3</v>
@@ -15188,7 +15188,7 @@
         <v>0</v>
       </c>
       <c r="T77" s="12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U77" s="12">
         <v>3</v>
@@ -15364,7 +15364,7 @@
         <v>0</v>
       </c>
       <c r="T78" s="12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U78" s="12">
         <v>3</v>
@@ -15540,7 +15540,7 @@
         <v>0</v>
       </c>
       <c r="T79" s="12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U79" s="12">
         <v>3</v>

--- a/servers/maze_main_server/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F044081-6DFA-42BF-92D3-82FA2347DC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E01BFF8-17BF-4122-BE98-24426D258985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_items_v8" sheetId="16" r:id="rId1"/>
@@ -538,7 +538,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="200">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1147,6 +1147,14 @@
   </si>
   <si>
     <t>暴击率+20%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>体力药剂</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用后恢复60点体力</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -1698,7 +1706,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:BF79"/>
+  <dimension ref="A1:BF80"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" bestFit="1" customWidth="1"/>
@@ -15657,6 +15665,182 @@
         <v>0</v>
       </c>
     </row>
+    <row r="80" spans="1:58" x14ac:dyDescent="0.15">
+      <c r="A80" s="1">
+        <v>49000001</v>
+      </c>
+      <c r="B80" s="1">
+        <v>490</v>
+      </c>
+      <c r="C80" s="1">
+        <v>1</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G80" s="1">
+        <v>0</v>
+      </c>
+      <c r="H80" s="1">
+        <v>0</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J80" s="4">
+        <v>48300001</v>
+      </c>
+      <c r="K80" s="1">
+        <v>5</v>
+      </c>
+      <c r="L80" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="M80" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="N80" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="O80" s="1">
+        <v>0</v>
+      </c>
+      <c r="P80" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="1">
+        <v>0</v>
+      </c>
+      <c r="R80" s="1">
+        <v>0</v>
+      </c>
+      <c r="S80" s="1">
+        <v>0</v>
+      </c>
+      <c r="T80" s="1">
+        <v>3</v>
+      </c>
+      <c r="U80" s="1">
+        <v>0</v>
+      </c>
+      <c r="V80" s="1">
+        <v>0</v>
+      </c>
+      <c r="W80" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="X80" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y80" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD80" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK80" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AL80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS80" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="AT80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV80" s="1">
+        <v>6</v>
+      </c>
+      <c r="AW80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AX80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AZ80" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA80" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB80" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC80" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD80" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE80" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF80" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A4:BE63" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="11" type="noConversion"/>

--- a/servers/maze_main_server/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E01BFF8-17BF-4122-BE98-24426D258985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA46957D-BD0D-4C9A-9B2C-1637ED6C3D01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_items_v8" sheetId="16" r:id="rId1"/>
@@ -538,7 +538,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="201">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1155,6 +1155,10 @@
   </si>
   <si>
     <t>使用后恢复60点体力</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>tiliping_icon</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -15690,11 +15694,11 @@
       <c r="H80" s="1">
         <v>0</v>
       </c>
-      <c r="I80" s="1" t="s">
+      <c r="I80" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="J80" s="4">
-        <v>48300001</v>
+      <c r="J80" s="4" t="s">
+        <v>200</v>
       </c>
       <c r="K80" s="1">
         <v>5</v>

--- a/servers/maze_main_server/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA46957D-BD0D-4C9A-9B2C-1637ED6C3D01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93EFB3B4-DF64-4796-8A8C-79EB86716159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_items_v8" sheetId="16" r:id="rId1"/>
@@ -538,7 +538,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1167" uniqueCount="207">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1159,6 +1159,30 @@
   </si>
   <si>
     <t>tiliping_icon</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>金币掉落展示道具</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>jinbidui</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>金币堆</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>强化水晶</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>强化水晶掉落展示道具</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>qianghuashidui</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -1391,7 +1415,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1419,6 +1443,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="2" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="差 2" xfId="6" xr:uid="{788C3904-E208-4A54-9251-FE59CA709635}"/>
@@ -1710,7 +1737,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:BF80"/>
+  <dimension ref="A1:BF82"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" bestFit="1" customWidth="1"/>
@@ -13207,19 +13234,19 @@
     </row>
     <row r="66" spans="1:58" x14ac:dyDescent="0.15">
       <c r="A66" s="1">
-        <v>46400001</v>
+        <v>46200002</v>
       </c>
       <c r="B66" s="1">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C66" s="1">
         <v>1</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>172</v>
+        <v>203</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>170</v>
@@ -13233,8 +13260,8 @@
       <c r="I66" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J66" s="1">
-        <v>44300001</v>
+      <c r="J66" s="13" t="s">
+        <v>202</v>
       </c>
       <c r="K66" s="1">
         <v>1</v>
@@ -13291,7 +13318,7 @@
         <v>0</v>
       </c>
       <c r="AC66" s="1">
-        <v>37850101</v>
+        <v>0</v>
       </c>
       <c r="AD66" s="1">
         <v>1</v>
@@ -13348,7 +13375,7 @@
         <v>0</v>
       </c>
       <c r="AV66" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AW66" s="1">
         <v>0</v>
@@ -13383,19 +13410,19 @@
     </row>
     <row r="67" spans="1:58" x14ac:dyDescent="0.15">
       <c r="A67" s="1">
-        <v>46500001</v>
+        <v>46400001</v>
       </c>
       <c r="B67" s="1">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C67" s="1">
         <v>1</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>170</v>
@@ -13410,7 +13437,7 @@
         <v>192</v>
       </c>
       <c r="J67" s="1">
-        <v>38500001</v>
+        <v>44300001</v>
       </c>
       <c r="K67" s="1">
         <v>1</v>
@@ -13559,25 +13586,25 @@
     </row>
     <row r="68" spans="1:58" x14ac:dyDescent="0.15">
       <c r="A68" s="1">
-        <v>46700001</v>
+        <v>46500001</v>
       </c>
       <c r="B68" s="1">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C68" s="1">
         <v>1</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>170</v>
       </c>
       <c r="G68" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68" s="1">
         <v>0</v>
@@ -13586,7 +13613,7 @@
         <v>192</v>
       </c>
       <c r="J68" s="1">
-        <v>45100001</v>
+        <v>38500001</v>
       </c>
       <c r="K68" s="1">
         <v>1</v>
@@ -13616,7 +13643,7 @@
         <v>0</v>
       </c>
       <c r="T68" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U68" s="1">
         <v>0</v>
@@ -13643,7 +13670,7 @@
         <v>0</v>
       </c>
       <c r="AC68" s="1">
-        <v>0</v>
+        <v>37850101</v>
       </c>
       <c r="AD68" s="1">
         <v>1</v>
@@ -13700,7 +13727,7 @@
         <v>0</v>
       </c>
       <c r="AV68" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AW68" s="1">
         <v>0</v>
@@ -13735,19 +13762,19 @@
     </row>
     <row r="69" spans="1:58" x14ac:dyDescent="0.15">
       <c r="A69" s="1">
-        <v>46800001</v>
+        <v>46700001</v>
       </c>
       <c r="B69" s="1">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C69" s="1">
         <v>1</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>170</v>
@@ -13762,7 +13789,7 @@
         <v>192</v>
       </c>
       <c r="J69" s="1">
-        <v>44500001</v>
+        <v>45100001</v>
       </c>
       <c r="K69" s="1">
         <v>1</v>
@@ -13819,7 +13846,7 @@
         <v>0</v>
       </c>
       <c r="AC69" s="1">
-        <v>37850101</v>
+        <v>0</v>
       </c>
       <c r="AD69" s="1">
         <v>1</v>
@@ -13876,7 +13903,7 @@
         <v>0</v>
       </c>
       <c r="AV69" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AW69" s="1">
         <v>0</v>
@@ -13911,19 +13938,19 @@
     </row>
     <row r="70" spans="1:58" x14ac:dyDescent="0.15">
       <c r="A70" s="1">
-        <v>46900001</v>
+        <v>46700002</v>
       </c>
       <c r="B70" s="1">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C70" s="1">
         <v>1</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>170</v>
@@ -13938,7 +13965,7 @@
         <v>192</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>167</v>
+        <v>206</v>
       </c>
       <c r="K70" s="1">
         <v>1</v>
@@ -13968,7 +13995,7 @@
         <v>0</v>
       </c>
       <c r="T70" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U70" s="1">
         <v>0</v>
@@ -13995,7 +14022,7 @@
         <v>0</v>
       </c>
       <c r="AC70" s="1">
-        <v>37850101</v>
+        <v>0</v>
       </c>
       <c r="AD70" s="1">
         <v>1</v>
@@ -14052,7 +14079,7 @@
         <v>0</v>
       </c>
       <c r="AV70" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AW70" s="1">
         <v>0</v>
@@ -14087,19 +14114,19 @@
     </row>
     <row r="71" spans="1:58" x14ac:dyDescent="0.15">
       <c r="A71" s="1">
-        <v>47000001</v>
+        <v>46800001</v>
       </c>
       <c r="B71" s="1">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C71" s="1">
         <v>1</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>170</v>
@@ -14114,7 +14141,7 @@
         <v>192</v>
       </c>
       <c r="J71" s="1">
-        <v>45600001</v>
+        <v>44500001</v>
       </c>
       <c r="K71" s="1">
         <v>1</v>
@@ -14144,7 +14171,7 @@
         <v>0</v>
       </c>
       <c r="T71" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U71" s="1">
         <v>0</v>
@@ -14263,25 +14290,25 @@
     </row>
     <row r="72" spans="1:58" x14ac:dyDescent="0.15">
       <c r="A72" s="1">
-        <v>47100001</v>
+        <v>46900001</v>
       </c>
       <c r="B72" s="1">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C72" s="1">
         <v>1</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>170</v>
       </c>
       <c r="G72" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72" s="1">
         <v>0</v>
@@ -14289,8 +14316,8 @@
       <c r="I72" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J72" s="1">
-        <v>44400001</v>
+      <c r="J72" s="1" t="s">
+        <v>167</v>
       </c>
       <c r="K72" s="1">
         <v>1</v>
@@ -14347,7 +14374,7 @@
         <v>0</v>
       </c>
       <c r="AC72" s="1">
-        <v>0</v>
+        <v>37850101</v>
       </c>
       <c r="AD72" s="1">
         <v>1</v>
@@ -14404,7 +14431,7 @@
         <v>0</v>
       </c>
       <c r="AV72" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AW72" s="1">
         <v>0</v>
@@ -14439,105 +14466,105 @@
     </row>
     <row r="73" spans="1:58" x14ac:dyDescent="0.15">
       <c r="A73" s="1">
-        <v>48200001</v>
+        <v>47000001</v>
       </c>
       <c r="B73" s="1">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="C73" s="1">
         <v>1</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="E73" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="F73" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="G73" s="12">
-        <v>0</v>
-      </c>
-      <c r="H73" s="12">
-        <v>0</v>
-      </c>
-      <c r="I73" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G73" s="1">
+        <v>0</v>
+      </c>
+      <c r="H73" s="1">
+        <v>0</v>
+      </c>
+      <c r="I73" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J73" s="4">
-        <v>48200001</v>
-      </c>
-      <c r="K73" s="12">
-        <v>5</v>
-      </c>
-      <c r="L73" s="12" t="s">
+      <c r="J73" s="1">
+        <v>45600001</v>
+      </c>
+      <c r="K73" s="1">
+        <v>1</v>
+      </c>
+      <c r="L73" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="M73" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="N73" s="12">
-        <v>0</v>
-      </c>
-      <c r="O73" s="12">
-        <v>0</v>
-      </c>
-      <c r="P73" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q73" s="12">
-        <v>0</v>
-      </c>
-      <c r="R73" s="12">
-        <v>0</v>
-      </c>
-      <c r="S73" s="12">
-        <v>0</v>
-      </c>
-      <c r="T73" s="12">
-        <v>0</v>
-      </c>
-      <c r="U73" s="12">
-        <v>3</v>
-      </c>
-      <c r="V73" s="12">
-        <v>0</v>
-      </c>
-      <c r="W73" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="X73" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="Y73" s="12">
-        <v>0</v>
-      </c>
-      <c r="Z73" s="12">
-        <v>0</v>
-      </c>
-      <c r="AA73" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB73" s="12">
-        <v>0</v>
-      </c>
-      <c r="AC73" s="12">
-        <v>0</v>
-      </c>
-      <c r="AD73" s="12">
-        <v>2</v>
-      </c>
-      <c r="AE73" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF73" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG73" s="12">
-        <v>0</v>
-      </c>
-      <c r="AH73" s="12">
+      <c r="M73" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="N73" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="O73" s="1">
+        <v>0</v>
+      </c>
+      <c r="P73" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="1">
+        <v>0</v>
+      </c>
+      <c r="R73" s="1">
+        <v>0</v>
+      </c>
+      <c r="S73" s="1">
+        <v>0</v>
+      </c>
+      <c r="T73" s="1">
+        <v>0</v>
+      </c>
+      <c r="U73" s="1">
+        <v>0</v>
+      </c>
+      <c r="V73" s="1">
+        <v>0</v>
+      </c>
+      <c r="W73" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="X73" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y73" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="1">
+        <v>37850101</v>
+      </c>
+      <c r="AD73" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="1">
         <v>0</v>
       </c>
       <c r="AI73" s="1">
@@ -14568,7 +14595,7 @@
         <v>0</v>
       </c>
       <c r="AR73" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AS73" s="1" t="s">
         <v>124</v>
@@ -14576,144 +14603,144 @@
       <c r="AT73" s="1">
         <v>0</v>
       </c>
-      <c r="AU73" s="12">
-        <v>0</v>
-      </c>
-      <c r="AV73" s="12">
-        <v>0</v>
-      </c>
-      <c r="AW73" s="12">
-        <v>0</v>
-      </c>
-      <c r="AX73" s="8">
-        <v>0</v>
-      </c>
-      <c r="AY73" s="8">
-        <v>0</v>
-      </c>
-      <c r="AZ73" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="BA73" s="10">
-        <v>0</v>
-      </c>
-      <c r="BB73" s="4">
-        <v>0</v>
-      </c>
-      <c r="BC73" s="4">
-        <v>0</v>
-      </c>
-      <c r="BD73" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="BE73" s="4">
-        <v>0</v>
-      </c>
-      <c r="BF73" s="4">
+      <c r="AU73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV73" s="1">
+        <v>3</v>
+      </c>
+      <c r="AW73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AX73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AZ73" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD73" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF73" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:58" x14ac:dyDescent="0.15">
       <c r="A74" s="1">
-        <v>48300001</v>
+        <v>47100001</v>
       </c>
       <c r="B74" s="1">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="C74" s="1">
         <v>1</v>
       </c>
-      <c r="D74" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="E74" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="F74" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="G74" s="12">
-        <v>0</v>
-      </c>
-      <c r="H74" s="12">
-        <v>0</v>
-      </c>
-      <c r="I74" s="4" t="s">
+      <c r="D74" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G74" s="1">
+        <v>1</v>
+      </c>
+      <c r="H74" s="1">
+        <v>0</v>
+      </c>
+      <c r="I74" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J74" s="4">
-        <v>48300001</v>
-      </c>
-      <c r="K74" s="12">
-        <v>5</v>
-      </c>
-      <c r="L74" s="12" t="s">
+      <c r="J74" s="1">
+        <v>44400001</v>
+      </c>
+      <c r="K74" s="1">
+        <v>1</v>
+      </c>
+      <c r="L74" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="M74" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="N74" s="12">
-        <v>0</v>
-      </c>
-      <c r="O74" s="12">
-        <v>0</v>
-      </c>
-      <c r="P74" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q74" s="12">
-        <v>0</v>
-      </c>
-      <c r="R74" s="12">
-        <v>0</v>
-      </c>
-      <c r="S74" s="12">
-        <v>0</v>
-      </c>
-      <c r="T74" s="12">
-        <v>0</v>
-      </c>
-      <c r="U74" s="12">
-        <v>3</v>
-      </c>
-      <c r="V74" s="12">
-        <v>0</v>
-      </c>
-      <c r="W74" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="X74" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="Y74" s="12">
-        <v>0</v>
-      </c>
-      <c r="Z74" s="12">
-        <v>0</v>
-      </c>
-      <c r="AA74" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB74" s="12">
-        <v>0</v>
-      </c>
-      <c r="AC74" s="12">
-        <v>0</v>
-      </c>
-      <c r="AD74" s="12">
-        <v>2</v>
-      </c>
-      <c r="AE74" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF74" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG74" s="12">
-        <v>0</v>
-      </c>
-      <c r="AH74" s="12">
+      <c r="M74" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="N74" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="O74" s="1">
+        <v>0</v>
+      </c>
+      <c r="P74" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="1">
+        <v>0</v>
+      </c>
+      <c r="R74" s="1">
+        <v>0</v>
+      </c>
+      <c r="S74" s="1">
+        <v>0</v>
+      </c>
+      <c r="T74" s="1">
+        <v>0</v>
+      </c>
+      <c r="U74" s="1">
+        <v>0</v>
+      </c>
+      <c r="V74" s="1">
+        <v>0</v>
+      </c>
+      <c r="W74" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="X74" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y74" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD74" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="1">
         <v>0</v>
       </c>
       <c r="AI74" s="1">
@@ -14744,7 +14771,7 @@
         <v>0</v>
       </c>
       <c r="AR74" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AS74" s="1" t="s">
         <v>124</v>
@@ -14752,58 +14779,58 @@
       <c r="AT74" s="1">
         <v>0</v>
       </c>
-      <c r="AU74" s="12">
-        <v>0</v>
-      </c>
-      <c r="AV74" s="12">
-        <v>0</v>
-      </c>
-      <c r="AW74" s="12">
-        <v>0</v>
-      </c>
-      <c r="AX74" s="8">
-        <v>0</v>
-      </c>
-      <c r="AY74" s="8">
-        <v>0</v>
-      </c>
-      <c r="AZ74" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="BA74" s="10">
-        <v>0</v>
-      </c>
-      <c r="BB74" s="4">
-        <v>0</v>
-      </c>
-      <c r="BC74" s="4">
-        <v>0</v>
-      </c>
-      <c r="BD74" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="BE74" s="4">
-        <v>0</v>
-      </c>
-      <c r="BF74" s="4">
+      <c r="AU74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV74" s="1">
+        <v>6</v>
+      </c>
+      <c r="AW74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AX74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AZ74" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA74" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB74" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC74" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD74" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE74" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF74" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:58" x14ac:dyDescent="0.15">
       <c r="A75" s="1">
-        <v>48300002</v>
+        <v>48200001</v>
       </c>
       <c r="B75" s="1">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C75" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F75" s="12" t="s">
         <v>166</v>
@@ -14818,7 +14845,7 @@
         <v>192</v>
       </c>
       <c r="J75" s="4">
-        <v>48300002</v>
+        <v>48200001</v>
       </c>
       <c r="K75" s="12">
         <v>5</v>
@@ -14967,19 +14994,19 @@
     </row>
     <row r="76" spans="1:58" x14ac:dyDescent="0.15">
       <c r="A76" s="1">
-        <v>48300003</v>
+        <v>48300001</v>
       </c>
       <c r="B76" s="1">
         <v>483</v>
       </c>
       <c r="C76" s="1">
-        <v>3</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>188</v>
+        <v>1</v>
+      </c>
+      <c r="D76" s="12" t="s">
+        <v>164</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>194</v>
+        <v>165</v>
       </c>
       <c r="F76" s="12" t="s">
         <v>166</v>
@@ -14994,7 +15021,7 @@
         <v>192</v>
       </c>
       <c r="J76" s="4">
-        <v>48300003</v>
+        <v>48300001</v>
       </c>
       <c r="K76" s="12">
         <v>5</v>
@@ -15143,19 +15170,19 @@
     </row>
     <row r="77" spans="1:58" x14ac:dyDescent="0.15">
       <c r="A77" s="1">
-        <v>48300004</v>
+        <v>48300002</v>
       </c>
       <c r="B77" s="1">
         <v>483</v>
       </c>
       <c r="C77" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F77" s="12" t="s">
         <v>166</v>
@@ -15170,7 +15197,7 @@
         <v>192</v>
       </c>
       <c r="J77" s="4">
-        <v>48300004</v>
+        <v>48300002</v>
       </c>
       <c r="K77" s="12">
         <v>5</v>
@@ -15319,19 +15346,19 @@
     </row>
     <row r="78" spans="1:58" x14ac:dyDescent="0.15">
       <c r="A78" s="1">
-        <v>48300005</v>
+        <v>48300003</v>
       </c>
       <c r="B78" s="1">
         <v>483</v>
       </c>
       <c r="C78" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F78" s="12" t="s">
         <v>166</v>
@@ -15346,7 +15373,7 @@
         <v>192</v>
       </c>
       <c r="J78" s="4">
-        <v>48300005</v>
+        <v>48300003</v>
       </c>
       <c r="K78" s="12">
         <v>5</v>
@@ -15495,19 +15522,19 @@
     </row>
     <row r="79" spans="1:58" x14ac:dyDescent="0.15">
       <c r="A79" s="1">
-        <v>48300006</v>
+        <v>48300004</v>
       </c>
       <c r="B79" s="1">
         <v>483</v>
       </c>
       <c r="C79" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F79" s="12" t="s">
         <v>166</v>
@@ -15522,7 +15549,7 @@
         <v>192</v>
       </c>
       <c r="J79" s="4">
-        <v>48300006</v>
+        <v>48300004</v>
       </c>
       <c r="K79" s="12">
         <v>5</v>
@@ -15671,105 +15698,105 @@
     </row>
     <row r="80" spans="1:58" x14ac:dyDescent="0.15">
       <c r="A80" s="1">
-        <v>49000001</v>
+        <v>48300005</v>
       </c>
       <c r="B80" s="1">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C80" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="G80" s="1">
-        <v>0</v>
-      </c>
-      <c r="H80" s="1">
+        <v>190</v>
+      </c>
+      <c r="E80" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="F80" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="G80" s="12">
+        <v>0</v>
+      </c>
+      <c r="H80" s="12">
         <v>0</v>
       </c>
       <c r="I80" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="J80" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="K80" s="1">
+      <c r="J80" s="4">
+        <v>48300005</v>
+      </c>
+      <c r="K80" s="12">
         <v>5</v>
       </c>
-      <c r="L80" s="1" t="s">
+      <c r="L80" s="12" t="s">
         <v>120</v>
       </c>
       <c r="M80" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="N80" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="O80" s="1">
-        <v>0</v>
-      </c>
-      <c r="P80" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q80" s="1">
-        <v>0</v>
-      </c>
-      <c r="R80" s="1">
-        <v>0</v>
-      </c>
-      <c r="S80" s="1">
-        <v>0</v>
-      </c>
-      <c r="T80" s="1">
+      <c r="N80" s="12">
+        <v>0</v>
+      </c>
+      <c r="O80" s="12">
+        <v>0</v>
+      </c>
+      <c r="P80" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="12">
+        <v>0</v>
+      </c>
+      <c r="R80" s="12">
+        <v>0</v>
+      </c>
+      <c r="S80" s="12">
+        <v>0</v>
+      </c>
+      <c r="T80" s="12">
+        <v>0</v>
+      </c>
+      <c r="U80" s="12">
         <v>3</v>
       </c>
-      <c r="U80" s="1">
-        <v>0</v>
-      </c>
-      <c r="V80" s="1">
-        <v>0</v>
-      </c>
-      <c r="W80" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="X80" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Y80" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z80" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA80" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB80" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC80" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD80" s="1">
-        <v>1</v>
-      </c>
-      <c r="AE80" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF80" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG80" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH80" s="1">
+      <c r="V80" s="12">
+        <v>0</v>
+      </c>
+      <c r="W80" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="X80" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y80" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z80" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA80" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB80" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC80" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD80" s="12">
+        <v>2</v>
+      </c>
+      <c r="AE80" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF80" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG80" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH80" s="12">
         <v>0</v>
       </c>
       <c r="AI80" s="1">
@@ -15800,7 +15827,7 @@
         <v>0</v>
       </c>
       <c r="AR80" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS80" s="1" t="s">
         <v>124</v>
@@ -15808,40 +15835,392 @@
       <c r="AT80" s="1">
         <v>0</v>
       </c>
-      <c r="AU80" s="1">
-        <v>0</v>
-      </c>
-      <c r="AV80" s="1">
+      <c r="AU80" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV80" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW80" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX80" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY80" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ80" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA80" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB80" s="4">
+        <v>0</v>
+      </c>
+      <c r="BC80" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD80" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE80" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF80" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:58" x14ac:dyDescent="0.15">
+      <c r="A81" s="1">
+        <v>48300006</v>
+      </c>
+      <c r="B81" s="1">
+        <v>483</v>
+      </c>
+      <c r="C81" s="1">
         <v>6</v>
       </c>
-      <c r="AW80" s="1">
-        <v>0</v>
-      </c>
-      <c r="AX80" s="1">
-        <v>0</v>
-      </c>
-      <c r="AY80" s="1">
-        <v>0</v>
-      </c>
-      <c r="AZ80" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="BA80" s="1">
-        <v>0</v>
-      </c>
-      <c r="BB80" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC80" s="1">
-        <v>0</v>
-      </c>
-      <c r="BD80" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="BE80" s="1">
-        <v>0</v>
-      </c>
-      <c r="BF80" s="1">
+      <c r="D81" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E81" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="F81" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="G81" s="12">
+        <v>0</v>
+      </c>
+      <c r="H81" s="12">
+        <v>0</v>
+      </c>
+      <c r="I81" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="J81" s="4">
+        <v>48300006</v>
+      </c>
+      <c r="K81" s="12">
+        <v>5</v>
+      </c>
+      <c r="L81" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M81" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="N81" s="12">
+        <v>0</v>
+      </c>
+      <c r="O81" s="12">
+        <v>0</v>
+      </c>
+      <c r="P81" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="12">
+        <v>0</v>
+      </c>
+      <c r="R81" s="12">
+        <v>0</v>
+      </c>
+      <c r="S81" s="12">
+        <v>0</v>
+      </c>
+      <c r="T81" s="12">
+        <v>0</v>
+      </c>
+      <c r="U81" s="12">
+        <v>3</v>
+      </c>
+      <c r="V81" s="12">
+        <v>0</v>
+      </c>
+      <c r="W81" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="X81" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y81" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB81" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC81" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD81" s="12">
+        <v>2</v>
+      </c>
+      <c r="AE81" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF81" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG81" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH81" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI81" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ81" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK81" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AL81" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM81" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN81" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO81" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP81" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ81" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR81" s="1">
+        <v>2</v>
+      </c>
+      <c r="AS81" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="AT81" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU81" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV81" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW81" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX81" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY81" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ81" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA81" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB81" s="4">
+        <v>0</v>
+      </c>
+      <c r="BC81" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD81" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE81" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF81" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:58" x14ac:dyDescent="0.15">
+      <c r="A82" s="1">
+        <v>49000001</v>
+      </c>
+      <c r="B82" s="1">
+        <v>490</v>
+      </c>
+      <c r="C82" s="1">
+        <v>1</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G82" s="1">
+        <v>0</v>
+      </c>
+      <c r="H82" s="1">
+        <v>0</v>
+      </c>
+      <c r="I82" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="J82" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="K82" s="1">
+        <v>5</v>
+      </c>
+      <c r="L82" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="M82" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="N82" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="O82" s="1">
+        <v>0</v>
+      </c>
+      <c r="P82" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="1">
+        <v>0</v>
+      </c>
+      <c r="R82" s="1">
+        <v>0</v>
+      </c>
+      <c r="S82" s="1">
+        <v>0</v>
+      </c>
+      <c r="T82" s="1">
+        <v>3</v>
+      </c>
+      <c r="U82" s="1">
+        <v>0</v>
+      </c>
+      <c r="V82" s="1">
+        <v>0</v>
+      </c>
+      <c r="W82" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="X82" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y82" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD82" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK82" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AL82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS82" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="AT82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV82" s="1">
+        <v>6</v>
+      </c>
+      <c r="AW82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AX82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AZ82" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA82" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB82" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC82" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD82" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE82" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF82" s="1">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93EFB3B4-DF64-4796-8A8C-79EB86716159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07738801-0A60-4B20-899B-C1FFFB3C3846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_items_v8" sheetId="16" r:id="rId1"/>
@@ -16128,7 +16128,7 @@
         <v>0</v>
       </c>
       <c r="AA82" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB82" s="1">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07738801-0A60-4B20-899B-C1FFFB3C3846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C8262C-E12D-4FEE-AC1F-DA913E569ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13234,7 +13234,7 @@
     </row>
     <row r="66" spans="1:58" x14ac:dyDescent="0.15">
       <c r="A66" s="1">
-        <v>46200002</v>
+        <v>46200101</v>
       </c>
       <c r="B66" s="1">
         <v>462</v>
@@ -13938,7 +13938,7 @@
     </row>
     <row r="70" spans="1:58" x14ac:dyDescent="0.15">
       <c r="A70" s="1">
-        <v>46700002</v>
+        <v>46700101</v>
       </c>
       <c r="B70" s="1">
         <v>467</v>

--- a/servers/maze_main_server/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C8262C-E12D-4FEE-AC1F-DA913E569ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B668B4-FDA4-4BF5-8A62-97187C8570CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="maze_items_v8" sheetId="16" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_items_v8!$A$4:$BE$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_items_v8!$A$4:$BE$82</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -645,9 +645,6 @@
     <t>sale_id_v2</t>
   </si>
   <si>
-    <t>is_bag</t>
-  </si>
-  <si>
     <t>fly_type</t>
   </si>
   <si>
@@ -1183,6 +1180,10 @@
   </si>
   <si>
     <t>qianghuashidui</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>is_bag</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -2141,7 +2142,7 @@
         <v>10</v>
       </c>
       <c r="BF2" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:58" x14ac:dyDescent="0.15">
@@ -2203,297 +2204,297 @@
         <v>34</v>
       </c>
       <c r="T3" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="U3" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="U3" s="6" t="s">
+      <c r="V3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="V3" s="6" t="s">
+      <c r="W3" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="W3" s="6" t="s">
+      <c r="X3" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="X3" s="7" t="s">
+      <c r="Y3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="Y3" s="6" t="s">
+      <c r="Z3" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="Z3" s="6" t="s">
+      <c r="AA3" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="AA3" s="6" t="s">
+      <c r="AB3" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="AB3" s="6" t="s">
+      <c r="AC3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="AC3" s="6" t="s">
+      <c r="AD3" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="AD3" s="6" t="s">
+      <c r="AE3" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="AE3" s="6" t="s">
+      <c r="AF3" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="AF3" s="6" t="s">
+      <c r="AG3" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="AG3" s="6" t="s">
+      <c r="AH3" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="AH3" s="6" t="s">
+      <c r="AI3" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AI3" s="3" t="s">
+      <c r="AJ3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="AJ3" s="3" t="s">
+      <c r="AK3" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="AK3" s="3" t="s">
+      <c r="AL3" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="AL3" s="3" t="s">
+      <c r="AM3" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="AM3" s="3" t="s">
+      <c r="AN3" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="AN3" s="3" t="s">
+      <c r="AO3" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="AO3" s="3" t="s">
+      <c r="AP3" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="AP3" s="3" t="s">
+      <c r="AQ3" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="AQ3" s="3" t="s">
+      <c r="AR3" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AR3" s="3" t="s">
+      <c r="AS3" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="AS3" s="3" t="s">
+      <c r="AT3" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="AT3" s="3" t="s">
+      <c r="AU3" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="AU3" s="7" t="s">
+      <c r="AV3" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AV3" s="2" t="s">
+      <c r="AW3" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AW3" s="2" t="s">
+      <c r="AX3" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="AX3" s="8" t="s">
+      <c r="AY3" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="AY3" s="8" t="s">
+      <c r="AZ3" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="AZ3" s="9" t="s">
+      <c r="BA3" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="BA3" s="10" t="s">
+      <c r="BB3" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="BB3" s="5" t="s">
+      <c r="BC3" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="BC3" s="5" t="s">
+      <c r="BD3" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="BD3" s="5" t="s">
+      <c r="BE3" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="BE3" s="5" t="s">
-        <v>72</v>
-      </c>
       <c r="BF3" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:58" x14ac:dyDescent="0.15">
       <c r="A4" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>74</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D4" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="F4" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="G4" s="6" t="s">
+      <c r="H4" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="I4" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="J4" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="K4" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="L4" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="M4" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="N4" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="O4" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="P4" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="Q4" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="Q4" s="6" t="s">
+      <c r="R4" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="R4" s="7" t="s">
+      <c r="S4" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="S4" s="7" t="s">
+      <c r="T4" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="T4" s="6" t="s">
+      <c r="U4" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="U4" s="6" t="s">
+      <c r="V4" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="V4" s="6" t="s">
+      <c r="W4" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="W4" s="6" t="s">
+      <c r="X4" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y4" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="X4" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="Y4" s="6" t="s">
+      <c r="Z4" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="Z4" s="6" t="s">
+      <c r="AA4" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="AA4" s="6" t="s">
+      <c r="AB4" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="AB4" s="6" t="s">
+      <c r="AC4" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="AC4" s="6" t="s">
+      <c r="AD4" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="AD4" s="6" t="s">
+      <c r="AE4" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="AE4" s="6" t="s">
+      <c r="AF4" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="AF4" s="6" t="s">
+      <c r="AG4" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="AG4" s="6" t="s">
+      <c r="AH4" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="AH4" s="6" t="s">
+      <c r="AI4" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="AI4" s="3" t="s">
+      <c r="AJ4" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="AJ4" s="3" t="s">
+      <c r="AK4" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="AK4" s="3" t="s">
+      <c r="AL4" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="AL4" s="3" t="s">
+      <c r="AM4" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="AM4" s="3" t="s">
+      <c r="AN4" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="AN4" s="3" t="s">
+      <c r="AO4" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="AO4" s="3" t="s">
+      <c r="AP4" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="AP4" s="3" t="s">
+      <c r="AQ4" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="AQ4" s="3" t="s">
+      <c r="AR4" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="AR4" s="3" t="s">
+      <c r="AS4" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="AS4" s="3" t="s">
+      <c r="AT4" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="AT4" s="3" t="s">
+      <c r="AU4" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="AV4" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="AU4" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="AV4" s="2" t="s">
+      <c r="AW4" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="AW4" s="2" t="s">
+      <c r="AX4" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY4" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="AZ4" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="BA4" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="BB4" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="AX4" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="AY4" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="AZ4" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="BA4" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="BB4" s="5" t="s">
+      <c r="BC4" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="BC4" s="5" t="s">
-        <v>119</v>
-      </c>
       <c r="BD4" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="BE4" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BF4" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:58" x14ac:dyDescent="0.15">
@@ -2507,37 +2508,37 @@
         <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G5" s="1">
-        <v>1</v>
-      </c>
-      <c r="H5" s="1">
-        <v>0</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="K5" s="1">
         <v>1</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O5" s="1">
         <v>0</v>
@@ -2564,10 +2565,10 @@
         <v>0</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y5" s="1">
         <v>0</v>
@@ -2630,7 +2631,7 @@
         <v>0</v>
       </c>
       <c r="AS5" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT5" s="1">
         <v>0</v>
@@ -2651,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="AZ5" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA5" s="1">
         <v>0</v>
@@ -2663,7 +2664,7 @@
         <v>0</v>
       </c>
       <c r="BD5" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE5" s="1">
         <v>0</v>
@@ -2683,37 +2684,37 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G6" s="1">
-        <v>1</v>
-      </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="K6" s="1">
         <v>1</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -2740,10 +2741,10 @@
         <v>0</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y6" s="1">
         <v>0</v>
@@ -2806,7 +2807,7 @@
         <v>0</v>
       </c>
       <c r="AS6" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT6" s="1">
         <v>0</v>
@@ -2827,7 +2828,7 @@
         <v>0</v>
       </c>
       <c r="AZ6" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA6" s="1">
         <v>0</v>
@@ -2839,7 +2840,7 @@
         <v>0</v>
       </c>
       <c r="BD6" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE6" s="1">
         <v>0</v>
@@ -2859,37 +2860,37 @@
         <v>4</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G7" s="1">
-        <v>1</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="K7" s="1">
         <v>1</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O7" s="1">
         <v>0</v>
@@ -2916,10 +2917,10 @@
         <v>0</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y7" s="1">
         <v>0</v>
@@ -2982,7 +2983,7 @@
         <v>0</v>
       </c>
       <c r="AS7" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT7" s="1">
         <v>0</v>
@@ -3003,7 +3004,7 @@
         <v>0</v>
       </c>
       <c r="AZ7" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA7" s="1">
         <v>0</v>
@@ -3015,7 +3016,7 @@
         <v>0</v>
       </c>
       <c r="BD7" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE7" s="1">
         <v>0</v>
@@ -3035,37 +3036,37 @@
         <v>5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F8" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G8" s="1">
-        <v>1</v>
-      </c>
-      <c r="H8" s="1">
-        <v>0</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="K8" s="1">
         <v>1</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O8" s="1">
         <v>0</v>
@@ -3092,10 +3093,10 @@
         <v>0</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X8" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y8" s="1">
         <v>0</v>
@@ -3158,7 +3159,7 @@
         <v>0</v>
       </c>
       <c r="AS8" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT8" s="1">
         <v>0</v>
@@ -3179,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="AZ8" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA8" s="1">
         <v>0</v>
@@ -3191,7 +3192,7 @@
         <v>0</v>
       </c>
       <c r="BD8" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE8" s="1">
         <v>0</v>
@@ -3211,37 +3212,37 @@
         <v>6</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F9" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G9" s="1">
-        <v>1</v>
-      </c>
-      <c r="H9" s="1">
-        <v>0</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="K9" s="1">
         <v>1</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O9" s="1">
         <v>0</v>
@@ -3268,10 +3269,10 @@
         <v>0</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X9" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y9" s="1">
         <v>0</v>
@@ -3334,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="AS9" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT9" s="1">
         <v>0</v>
@@ -3355,7 +3356,7 @@
         <v>0</v>
       </c>
       <c r="AZ9" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA9" s="1">
         <v>0</v>
@@ -3367,7 +3368,7 @@
         <v>0</v>
       </c>
       <c r="BD9" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE9" s="1">
         <v>0</v>
@@ -3387,37 +3388,37 @@
         <v>7</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F10" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G10" s="1">
-        <v>1</v>
-      </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="K10" s="1">
         <v>1</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O10" s="1">
         <v>0</v>
@@ -3444,10 +3445,10 @@
         <v>0</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X10" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y10" s="1">
         <v>0</v>
@@ -3510,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="AS10" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT10" s="1">
         <v>0</v>
@@ -3531,7 +3532,7 @@
         <v>0</v>
       </c>
       <c r="AZ10" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA10" s="1">
         <v>0</v>
@@ -3543,7 +3544,7 @@
         <v>0</v>
       </c>
       <c r="BD10" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE10" s="1">
         <v>0</v>
@@ -3563,37 +3564,37 @@
         <v>8</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F11" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="J11" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G11" s="1">
-        <v>1</v>
-      </c>
-      <c r="H11" s="1">
-        <v>0</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="K11" s="1">
         <v>1</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O11" s="1">
         <v>0</v>
@@ -3620,10 +3621,10 @@
         <v>0</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X11" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y11" s="1">
         <v>0</v>
@@ -3686,7 +3687,7 @@
         <v>0</v>
       </c>
       <c r="AS11" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT11" s="1">
         <v>0</v>
@@ -3707,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="AZ11" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA11" s="1">
         <v>0</v>
@@ -3719,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="BD11" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE11" s="1">
         <v>0</v>
@@ -3739,37 +3740,37 @@
         <v>9</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F12" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J12" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G12" s="1">
-        <v>1</v>
-      </c>
-      <c r="H12" s="1">
-        <v>0</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="K12" s="1">
         <v>1</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O12" s="1">
         <v>0</v>
@@ -3796,10 +3797,10 @@
         <v>0</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X12" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y12" s="1">
         <v>0</v>
@@ -3862,7 +3863,7 @@
         <v>0</v>
       </c>
       <c r="AS12" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT12" s="1">
         <v>0</v>
@@ -3883,7 +3884,7 @@
         <v>0</v>
       </c>
       <c r="AZ12" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA12" s="1">
         <v>0</v>
@@ -3895,7 +3896,7 @@
         <v>0</v>
       </c>
       <c r="BD12" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE12" s="1">
         <v>0</v>
@@ -3915,37 +3916,37 @@
         <v>10</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F13" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J13" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G13" s="1">
-        <v>1</v>
-      </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="K13" s="1">
         <v>1</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O13" s="1">
         <v>0</v>
@@ -3972,10 +3973,10 @@
         <v>0</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X13" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y13" s="1">
         <v>0</v>
@@ -4038,7 +4039,7 @@
         <v>0</v>
       </c>
       <c r="AS13" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT13" s="1">
         <v>0</v>
@@ -4059,7 +4060,7 @@
         <v>0</v>
       </c>
       <c r="AZ13" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA13" s="1">
         <v>0</v>
@@ -4071,7 +4072,7 @@
         <v>0</v>
       </c>
       <c r="BD13" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE13" s="1">
         <v>0</v>
@@ -4091,37 +4092,37 @@
         <v>11</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F14" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J14" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G14" s="1">
-        <v>1</v>
-      </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="K14" s="1">
         <v>1</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O14" s="1">
         <v>0</v>
@@ -4148,10 +4149,10 @@
         <v>0</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y14" s="1">
         <v>0</v>
@@ -4214,7 +4215,7 @@
         <v>0</v>
       </c>
       <c r="AS14" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT14" s="1">
         <v>0</v>
@@ -4235,7 +4236,7 @@
         <v>0</v>
       </c>
       <c r="AZ14" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA14" s="1">
         <v>0</v>
@@ -4247,7 +4248,7 @@
         <v>0</v>
       </c>
       <c r="BD14" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE14" s="1">
         <v>0</v>
@@ -4267,37 +4268,37 @@
         <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F15" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J15" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G15" s="1">
-        <v>1</v>
-      </c>
-      <c r="H15" s="1">
-        <v>0</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="K15" s="1">
         <v>1</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O15" s="1">
         <v>0</v>
@@ -4324,10 +4325,10 @@
         <v>0</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X15" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y15" s="1">
         <v>0</v>
@@ -4390,7 +4391,7 @@
         <v>0</v>
       </c>
       <c r="AS15" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT15" s="1">
         <v>0</v>
@@ -4411,7 +4412,7 @@
         <v>0</v>
       </c>
       <c r="AZ15" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA15" s="1">
         <v>0</v>
@@ -4423,7 +4424,7 @@
         <v>0</v>
       </c>
       <c r="BD15" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE15" s="1">
         <v>0</v>
@@ -4443,37 +4444,37 @@
         <v>13</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F16" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J16" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G16" s="1">
-        <v>1</v>
-      </c>
-      <c r="H16" s="1">
-        <v>0</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="K16" s="1">
         <v>1</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O16" s="1">
         <v>0</v>
@@ -4500,10 +4501,10 @@
         <v>0</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X16" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y16" s="1">
         <v>0</v>
@@ -4566,7 +4567,7 @@
         <v>0</v>
       </c>
       <c r="AS16" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT16" s="1">
         <v>0</v>
@@ -4587,7 +4588,7 @@
         <v>0</v>
       </c>
       <c r="AZ16" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA16" s="1">
         <v>0</v>
@@ -4599,7 +4600,7 @@
         <v>0</v>
       </c>
       <c r="BD16" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE16" s="1">
         <v>0</v>
@@ -4619,37 +4620,37 @@
         <v>14</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F17" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J17" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G17" s="1">
-        <v>1</v>
-      </c>
-      <c r="H17" s="1">
-        <v>0</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="K17" s="1">
         <v>1</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O17" s="1">
         <v>0</v>
@@ -4676,10 +4677,10 @@
         <v>0</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X17" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y17" s="1">
         <v>0</v>
@@ -4742,7 +4743,7 @@
         <v>0</v>
       </c>
       <c r="AS17" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT17" s="1">
         <v>0</v>
@@ -4763,7 +4764,7 @@
         <v>0</v>
       </c>
       <c r="AZ17" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA17" s="1">
         <v>0</v>
@@ -4775,7 +4776,7 @@
         <v>0</v>
       </c>
       <c r="BD17" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE17" s="1">
         <v>0</v>
@@ -4795,37 +4796,37 @@
         <v>15</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F18" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J18" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G18" s="1">
-        <v>1</v>
-      </c>
-      <c r="H18" s="1">
-        <v>0</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="K18" s="1">
         <v>1</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O18" s="1">
         <v>0</v>
@@ -4852,10 +4853,10 @@
         <v>0</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X18" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y18" s="1">
         <v>0</v>
@@ -4918,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="AS18" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT18" s="1">
         <v>0</v>
@@ -4939,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="AZ18" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA18" s="1">
         <v>0</v>
@@ -4951,7 +4952,7 @@
         <v>0</v>
       </c>
       <c r="BD18" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE18" s="1">
         <v>0</v>
@@ -4971,37 +4972,37 @@
         <v>16</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F19" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J19" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G19" s="1">
-        <v>1</v>
-      </c>
-      <c r="H19" s="1">
-        <v>0</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="K19" s="1">
         <v>1</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O19" s="1">
         <v>0</v>
@@ -5028,10 +5029,10 @@
         <v>0</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X19" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y19" s="1">
         <v>0</v>
@@ -5094,7 +5095,7 @@
         <v>0</v>
       </c>
       <c r="AS19" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT19" s="1">
         <v>0</v>
@@ -5115,7 +5116,7 @@
         <v>0</v>
       </c>
       <c r="AZ19" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA19" s="1">
         <v>0</v>
@@ -5127,7 +5128,7 @@
         <v>0</v>
       </c>
       <c r="BD19" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE19" s="1">
         <v>0</v>
@@ -5147,37 +5148,37 @@
         <v>17</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F20" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G20" s="1">
+        <v>1</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J20" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G20" s="1">
-        <v>1</v>
-      </c>
-      <c r="H20" s="1">
-        <v>0</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="K20" s="1">
         <v>1</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O20" s="1">
         <v>0</v>
@@ -5204,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X20" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y20" s="1">
         <v>0</v>
@@ -5270,7 +5271,7 @@
         <v>0</v>
       </c>
       <c r="AS20" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT20" s="1">
         <v>0</v>
@@ -5291,7 +5292,7 @@
         <v>0</v>
       </c>
       <c r="AZ20" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA20" s="1">
         <v>0</v>
@@ -5303,7 +5304,7 @@
         <v>0</v>
       </c>
       <c r="BD20" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE20" s="1">
         <v>0</v>
@@ -5323,37 +5324,37 @@
         <v>18</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F21" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G21" s="1">
+        <v>1</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J21" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G21" s="1">
-        <v>1</v>
-      </c>
-      <c r="H21" s="1">
-        <v>0</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="K21" s="1">
         <v>1</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O21" s="1">
         <v>0</v>
@@ -5380,10 +5381,10 @@
         <v>0</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X21" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y21" s="1">
         <v>0</v>
@@ -5446,7 +5447,7 @@
         <v>0</v>
       </c>
       <c r="AS21" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT21" s="1">
         <v>0</v>
@@ -5467,7 +5468,7 @@
         <v>0</v>
       </c>
       <c r="AZ21" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA21" s="1">
         <v>0</v>
@@ -5479,7 +5480,7 @@
         <v>0</v>
       </c>
       <c r="BD21" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE21" s="1">
         <v>0</v>
@@ -5499,37 +5500,37 @@
         <v>19</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F22" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G22" s="1">
+        <v>1</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J22" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G22" s="1">
-        <v>1</v>
-      </c>
-      <c r="H22" s="1">
-        <v>0</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="K22" s="1">
         <v>1</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O22" s="1">
         <v>0</v>
@@ -5556,10 +5557,10 @@
         <v>0</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X22" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y22" s="1">
         <v>0</v>
@@ -5622,7 +5623,7 @@
         <v>0</v>
       </c>
       <c r="AS22" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT22" s="1">
         <v>0</v>
@@ -5643,7 +5644,7 @@
         <v>0</v>
       </c>
       <c r="AZ22" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA22" s="1">
         <v>0</v>
@@ -5655,7 +5656,7 @@
         <v>0</v>
       </c>
       <c r="BD22" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE22" s="1">
         <v>0</v>
@@ -5675,37 +5676,37 @@
         <v>20</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F23" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G23" s="1">
+        <v>1</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J23" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G23" s="1">
-        <v>1</v>
-      </c>
-      <c r="H23" s="1">
-        <v>0</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="K23" s="1">
         <v>1</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O23" s="1">
         <v>0</v>
@@ -5732,10 +5733,10 @@
         <v>0</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X23" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y23" s="1">
         <v>0</v>
@@ -5798,7 +5799,7 @@
         <v>0</v>
       </c>
       <c r="AS23" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT23" s="1">
         <v>0</v>
@@ -5819,7 +5820,7 @@
         <v>0</v>
       </c>
       <c r="AZ23" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA23" s="1">
         <v>0</v>
@@ -5831,7 +5832,7 @@
         <v>0</v>
       </c>
       <c r="BD23" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE23" s="1">
         <v>0</v>
@@ -5851,37 +5852,37 @@
         <v>21</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F24" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G24" s="1">
+        <v>1</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J24" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G24" s="1">
-        <v>1</v>
-      </c>
-      <c r="H24" s="1">
-        <v>0</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="K24" s="1">
         <v>1</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O24" s="1">
         <v>0</v>
@@ -5908,10 +5909,10 @@
         <v>0</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X24" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y24" s="1">
         <v>0</v>
@@ -5974,7 +5975,7 @@
         <v>0</v>
       </c>
       <c r="AS24" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT24" s="1">
         <v>0</v>
@@ -5995,7 +5996,7 @@
         <v>0</v>
       </c>
       <c r="AZ24" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA24" s="1">
         <v>0</v>
@@ -6007,7 +6008,7 @@
         <v>0</v>
       </c>
       <c r="BD24" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE24" s="1">
         <v>0</v>
@@ -6027,37 +6028,37 @@
         <v>22</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F25" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G25" s="1">
+        <v>1</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J25" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G25" s="1">
-        <v>1</v>
-      </c>
-      <c r="H25" s="1">
-        <v>0</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="K25" s="1">
         <v>1</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O25" s="1">
         <v>0</v>
@@ -6084,10 +6085,10 @@
         <v>0</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X25" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y25" s="1">
         <v>0</v>
@@ -6150,7 +6151,7 @@
         <v>0</v>
       </c>
       <c r="AS25" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT25" s="1">
         <v>0</v>
@@ -6171,7 +6172,7 @@
         <v>0</v>
       </c>
       <c r="AZ25" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA25" s="1">
         <v>0</v>
@@ -6183,7 +6184,7 @@
         <v>0</v>
       </c>
       <c r="BD25" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE25" s="1">
         <v>0</v>
@@ -6203,37 +6204,37 @@
         <v>23</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F26" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G26" s="1">
+        <v>1</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J26" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G26" s="1">
-        <v>1</v>
-      </c>
-      <c r="H26" s="1">
-        <v>0</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="K26" s="1">
         <v>1</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O26" s="1">
         <v>0</v>
@@ -6260,10 +6261,10 @@
         <v>0</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X26" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y26" s="1">
         <v>0</v>
@@ -6326,7 +6327,7 @@
         <v>0</v>
       </c>
       <c r="AS26" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT26" s="1">
         <v>0</v>
@@ -6347,7 +6348,7 @@
         <v>0</v>
       </c>
       <c r="AZ26" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA26" s="1">
         <v>0</v>
@@ -6359,7 +6360,7 @@
         <v>0</v>
       </c>
       <c r="BD26" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE26" s="1">
         <v>0</v>
@@ -6379,37 +6380,37 @@
         <v>24</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F27" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G27" s="1">
+        <v>1</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J27" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G27" s="1">
-        <v>1</v>
-      </c>
-      <c r="H27" s="1">
-        <v>0</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="K27" s="1">
         <v>1</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O27" s="1">
         <v>0</v>
@@ -6436,10 +6437,10 @@
         <v>0</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X27" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y27" s="1">
         <v>0</v>
@@ -6502,7 +6503,7 @@
         <v>0</v>
       </c>
       <c r="AS27" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT27" s="1">
         <v>0</v>
@@ -6523,7 +6524,7 @@
         <v>0</v>
       </c>
       <c r="AZ27" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA27" s="1">
         <v>0</v>
@@ -6535,7 +6536,7 @@
         <v>0</v>
       </c>
       <c r="BD27" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE27" s="1">
         <v>0</v>
@@ -6555,37 +6556,37 @@
         <v>25</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F28" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G28" s="1">
+        <v>1</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J28" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G28" s="1">
-        <v>1</v>
-      </c>
-      <c r="H28" s="1">
-        <v>0</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="K28" s="1">
         <v>1</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O28" s="1">
         <v>0</v>
@@ -6612,10 +6613,10 @@
         <v>0</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X28" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y28" s="1">
         <v>0</v>
@@ -6678,7 +6679,7 @@
         <v>0</v>
       </c>
       <c r="AS28" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT28" s="1">
         <v>0</v>
@@ -6699,7 +6700,7 @@
         <v>0</v>
       </c>
       <c r="AZ28" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA28" s="1">
         <v>0</v>
@@ -6711,7 +6712,7 @@
         <v>0</v>
       </c>
       <c r="BD28" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE28" s="1">
         <v>0</v>
@@ -6731,37 +6732,37 @@
         <v>26</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F29" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G29" s="1">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J29" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G29" s="1">
-        <v>1</v>
-      </c>
-      <c r="H29" s="1">
-        <v>0</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="K29" s="1">
         <v>1</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O29" s="1">
         <v>0</v>
@@ -6788,10 +6789,10 @@
         <v>0</v>
       </c>
       <c r="W29" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X29" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y29" s="1">
         <v>0</v>
@@ -6854,7 +6855,7 @@
         <v>0</v>
       </c>
       <c r="AS29" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT29" s="1">
         <v>0</v>
@@ -6875,7 +6876,7 @@
         <v>0</v>
       </c>
       <c r="AZ29" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA29" s="1">
         <v>0</v>
@@ -6887,7 +6888,7 @@
         <v>0</v>
       </c>
       <c r="BD29" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE29" s="1">
         <v>0</v>
@@ -6907,37 +6908,37 @@
         <v>27</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F30" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G30" s="1">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1">
+        <v>0</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J30" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G30" s="1">
-        <v>1</v>
-      </c>
-      <c r="H30" s="1">
-        <v>0</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="K30" s="1">
         <v>1</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O30" s="1">
         <v>0</v>
@@ -6964,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X30" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y30" s="1">
         <v>0</v>
@@ -7030,7 +7031,7 @@
         <v>0</v>
       </c>
       <c r="AS30" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT30" s="1">
         <v>0</v>
@@ -7051,7 +7052,7 @@
         <v>0</v>
       </c>
       <c r="AZ30" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA30" s="1">
         <v>0</v>
@@ -7063,7 +7064,7 @@
         <v>0</v>
       </c>
       <c r="BD30" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE30" s="1">
         <v>0</v>
@@ -7083,37 +7084,37 @@
         <v>28</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F31" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G31" s="1">
+        <v>1</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J31" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G31" s="1">
-        <v>1</v>
-      </c>
-      <c r="H31" s="1">
-        <v>0</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="K31" s="1">
         <v>1</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O31" s="1">
         <v>0</v>
@@ -7140,10 +7141,10 @@
         <v>0</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X31" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y31" s="1">
         <v>0</v>
@@ -7206,7 +7207,7 @@
         <v>0</v>
       </c>
       <c r="AS31" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT31" s="1">
         <v>0</v>
@@ -7227,7 +7228,7 @@
         <v>0</v>
       </c>
       <c r="AZ31" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA31" s="1">
         <v>0</v>
@@ -7239,7 +7240,7 @@
         <v>0</v>
       </c>
       <c r="BD31" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE31" s="1">
         <v>0</v>
@@ -7259,37 +7260,37 @@
         <v>29</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F32" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G32" s="1">
+        <v>1</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J32" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G32" s="1">
-        <v>1</v>
-      </c>
-      <c r="H32" s="1">
-        <v>0</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="K32" s="1">
         <v>1</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O32" s="1">
         <v>0</v>
@@ -7316,10 +7317,10 @@
         <v>0</v>
       </c>
       <c r="W32" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X32" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y32" s="1">
         <v>0</v>
@@ -7382,7 +7383,7 @@
         <v>0</v>
       </c>
       <c r="AS32" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT32" s="1">
         <v>0</v>
@@ -7403,7 +7404,7 @@
         <v>0</v>
       </c>
       <c r="AZ32" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA32" s="1">
         <v>0</v>
@@ -7415,7 +7416,7 @@
         <v>0</v>
       </c>
       <c r="BD32" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE32" s="1">
         <v>0</v>
@@ -7435,37 +7436,37 @@
         <v>30</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F33" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G33" s="1">
+        <v>1</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J33" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G33" s="1">
-        <v>1</v>
-      </c>
-      <c r="H33" s="1">
-        <v>0</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="K33" s="1">
         <v>1</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O33" s="1">
         <v>0</v>
@@ -7492,10 +7493,10 @@
         <v>0</v>
       </c>
       <c r="W33" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X33" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y33" s="1">
         <v>0</v>
@@ -7558,7 +7559,7 @@
         <v>0</v>
       </c>
       <c r="AS33" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT33" s="1">
         <v>0</v>
@@ -7579,7 +7580,7 @@
         <v>0</v>
       </c>
       <c r="AZ33" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA33" s="1">
         <v>0</v>
@@ -7591,7 +7592,7 @@
         <v>0</v>
       </c>
       <c r="BD33" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE33" s="1">
         <v>0</v>
@@ -7611,14 +7612,14 @@
         <v>1</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>134</v>
-      </c>
       <c r="G34" s="1">
         <v>1</v>
       </c>
@@ -7626,22 +7627,22 @@
         <v>0</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K34" s="1">
         <v>1</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O34" s="1">
         <v>0</v>
@@ -7668,10 +7669,10 @@
         <v>0</v>
       </c>
       <c r="W34" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X34" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y34" s="1">
         <v>0</v>
@@ -7734,7 +7735,7 @@
         <v>0</v>
       </c>
       <c r="AS34" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT34" s="1">
         <v>0</v>
@@ -7755,7 +7756,7 @@
         <v>0</v>
       </c>
       <c r="AZ34" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA34" s="1">
         <v>0</v>
@@ -7767,7 +7768,7 @@
         <v>0</v>
       </c>
       <c r="BD34" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE34" s="1">
         <v>0</v>
@@ -7787,13 +7788,13 @@
         <v>2</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G35" s="1">
         <v>1</v>
@@ -7802,22 +7803,22 @@
         <v>0</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K35" s="1">
         <v>1</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O35" s="1">
         <v>0</v>
@@ -7844,10 +7845,10 @@
         <v>0</v>
       </c>
       <c r="W35" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X35" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y35" s="1">
         <v>0</v>
@@ -7910,7 +7911,7 @@
         <v>0</v>
       </c>
       <c r="AS35" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT35" s="1">
         <v>0</v>
@@ -7931,7 +7932,7 @@
         <v>0</v>
       </c>
       <c r="AZ35" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA35" s="1">
         <v>0</v>
@@ -7943,7 +7944,7 @@
         <v>0</v>
       </c>
       <c r="BD35" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE35" s="1">
         <v>0</v>
@@ -7963,13 +7964,13 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G36" s="1">
         <v>1</v>
@@ -7978,22 +7979,22 @@
         <v>0</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K36" s="1">
         <v>1</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O36" s="1">
         <v>0</v>
@@ -8020,10 +8021,10 @@
         <v>0</v>
       </c>
       <c r="W36" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X36" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y36" s="1">
         <v>0</v>
@@ -8086,7 +8087,7 @@
         <v>0</v>
       </c>
       <c r="AS36" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT36" s="1">
         <v>0</v>
@@ -8107,7 +8108,7 @@
         <v>0</v>
       </c>
       <c r="AZ36" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA36" s="1">
         <v>0</v>
@@ -8119,7 +8120,7 @@
         <v>0</v>
       </c>
       <c r="BD36" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE36" s="1">
         <v>0</v>
@@ -8139,13 +8140,13 @@
         <v>4</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G37" s="1">
         <v>1</v>
@@ -8154,22 +8155,22 @@
         <v>0</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K37" s="1">
         <v>1</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O37" s="1">
         <v>0</v>
@@ -8196,10 +8197,10 @@
         <v>0</v>
       </c>
       <c r="W37" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X37" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y37" s="1">
         <v>0</v>
@@ -8262,7 +8263,7 @@
         <v>0</v>
       </c>
       <c r="AS37" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT37" s="1">
         <v>0</v>
@@ -8283,7 +8284,7 @@
         <v>0</v>
       </c>
       <c r="AZ37" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA37" s="1">
         <v>0</v>
@@ -8295,7 +8296,7 @@
         <v>0</v>
       </c>
       <c r="BD37" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE37" s="1">
         <v>0</v>
@@ -8315,13 +8316,13 @@
         <v>5</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G38" s="1">
         <v>1</v>
@@ -8330,22 +8331,22 @@
         <v>0</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K38" s="1">
         <v>1</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O38" s="1">
         <v>0</v>
@@ -8372,10 +8373,10 @@
         <v>0</v>
       </c>
       <c r="W38" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X38" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y38" s="1">
         <v>0</v>
@@ -8438,7 +8439,7 @@
         <v>0</v>
       </c>
       <c r="AS38" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT38" s="1">
         <v>0</v>
@@ -8459,7 +8460,7 @@
         <v>0</v>
       </c>
       <c r="AZ38" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA38" s="1">
         <v>0</v>
@@ -8471,7 +8472,7 @@
         <v>0</v>
       </c>
       <c r="BD38" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE38" s="1">
         <v>0</v>
@@ -8491,13 +8492,13 @@
         <v>6</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G39" s="1">
         <v>1</v>
@@ -8506,22 +8507,22 @@
         <v>0</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K39" s="1">
         <v>1</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O39" s="1">
         <v>0</v>
@@ -8548,10 +8549,10 @@
         <v>0</v>
       </c>
       <c r="W39" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X39" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y39" s="1">
         <v>0</v>
@@ -8614,7 +8615,7 @@
         <v>0</v>
       </c>
       <c r="AS39" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT39" s="1">
         <v>0</v>
@@ -8635,7 +8636,7 @@
         <v>0</v>
       </c>
       <c r="AZ39" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA39" s="1">
         <v>0</v>
@@ -8647,7 +8648,7 @@
         <v>0</v>
       </c>
       <c r="BD39" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE39" s="1">
         <v>0</v>
@@ -8667,13 +8668,13 @@
         <v>7</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G40" s="1">
         <v>1</v>
@@ -8682,22 +8683,22 @@
         <v>0</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K40" s="1">
         <v>1</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O40" s="1">
         <v>0</v>
@@ -8724,10 +8725,10 @@
         <v>0</v>
       </c>
       <c r="W40" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X40" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y40" s="1">
         <v>0</v>
@@ -8790,7 +8791,7 @@
         <v>0</v>
       </c>
       <c r="AS40" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT40" s="1">
         <v>0</v>
@@ -8811,7 +8812,7 @@
         <v>0</v>
       </c>
       <c r="AZ40" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA40" s="1">
         <v>0</v>
@@ -8823,7 +8824,7 @@
         <v>0</v>
       </c>
       <c r="BD40" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE40" s="1">
         <v>0</v>
@@ -8843,13 +8844,13 @@
         <v>8</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G41" s="1">
         <v>1</v>
@@ -8858,22 +8859,22 @@
         <v>0</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K41" s="1">
         <v>1</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O41" s="1">
         <v>0</v>
@@ -8900,10 +8901,10 @@
         <v>0</v>
       </c>
       <c r="W41" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X41" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y41" s="1">
         <v>0</v>
@@ -8966,7 +8967,7 @@
         <v>0</v>
       </c>
       <c r="AS41" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT41" s="1">
         <v>0</v>
@@ -8987,7 +8988,7 @@
         <v>0</v>
       </c>
       <c r="AZ41" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA41" s="1">
         <v>0</v>
@@ -8999,7 +9000,7 @@
         <v>0</v>
       </c>
       <c r="BD41" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE41" s="1">
         <v>0</v>
@@ -9019,13 +9020,13 @@
         <v>9</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G42" s="1">
         <v>1</v>
@@ -9034,22 +9035,22 @@
         <v>0</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K42" s="1">
         <v>1</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O42" s="1">
         <v>0</v>
@@ -9076,10 +9077,10 @@
         <v>0</v>
       </c>
       <c r="W42" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X42" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y42" s="1">
         <v>0</v>
@@ -9142,7 +9143,7 @@
         <v>0</v>
       </c>
       <c r="AS42" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT42" s="1">
         <v>0</v>
@@ -9163,7 +9164,7 @@
         <v>0</v>
       </c>
       <c r="AZ42" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA42" s="1">
         <v>0</v>
@@ -9175,7 +9176,7 @@
         <v>0</v>
       </c>
       <c r="BD42" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE42" s="1">
         <v>0</v>
@@ -9195,13 +9196,13 @@
         <v>10</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G43" s="1">
         <v>1</v>
@@ -9210,22 +9211,22 @@
         <v>0</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K43" s="1">
         <v>1</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O43" s="1">
         <v>0</v>
@@ -9252,10 +9253,10 @@
         <v>0</v>
       </c>
       <c r="W43" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X43" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y43" s="1">
         <v>0</v>
@@ -9318,7 +9319,7 @@
         <v>0</v>
       </c>
       <c r="AS43" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT43" s="1">
         <v>0</v>
@@ -9339,7 +9340,7 @@
         <v>0</v>
       </c>
       <c r="AZ43" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA43" s="1">
         <v>0</v>
@@ -9351,7 +9352,7 @@
         <v>0</v>
       </c>
       <c r="BD43" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE43" s="1">
         <v>0</v>
@@ -9371,13 +9372,13 @@
         <v>11</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G44" s="1">
         <v>1</v>
@@ -9386,22 +9387,22 @@
         <v>0</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K44" s="1">
         <v>1</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O44" s="1">
         <v>0</v>
@@ -9428,10 +9429,10 @@
         <v>0</v>
       </c>
       <c r="W44" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X44" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y44" s="1">
         <v>0</v>
@@ -9494,7 +9495,7 @@
         <v>0</v>
       </c>
       <c r="AS44" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT44" s="1">
         <v>0</v>
@@ -9515,7 +9516,7 @@
         <v>0</v>
       </c>
       <c r="AZ44" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA44" s="1">
         <v>0</v>
@@ -9527,7 +9528,7 @@
         <v>0</v>
       </c>
       <c r="BD44" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE44" s="1">
         <v>0</v>
@@ -9547,13 +9548,13 @@
         <v>12</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G45" s="1">
         <v>1</v>
@@ -9562,22 +9563,22 @@
         <v>0</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K45" s="1">
         <v>1</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O45" s="1">
         <v>0</v>
@@ -9604,10 +9605,10 @@
         <v>0</v>
       </c>
       <c r="W45" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X45" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y45" s="1">
         <v>0</v>
@@ -9670,7 +9671,7 @@
         <v>0</v>
       </c>
       <c r="AS45" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT45" s="1">
         <v>0</v>
@@ -9691,7 +9692,7 @@
         <v>0</v>
       </c>
       <c r="AZ45" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA45" s="1">
         <v>0</v>
@@ -9703,7 +9704,7 @@
         <v>0</v>
       </c>
       <c r="BD45" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE45" s="1">
         <v>0</v>
@@ -9723,13 +9724,13 @@
         <v>13</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G46" s="1">
         <v>1</v>
@@ -9738,22 +9739,22 @@
         <v>0</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K46" s="1">
         <v>1</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O46" s="1">
         <v>0</v>
@@ -9780,10 +9781,10 @@
         <v>0</v>
       </c>
       <c r="W46" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X46" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y46" s="1">
         <v>0</v>
@@ -9846,7 +9847,7 @@
         <v>0</v>
       </c>
       <c r="AS46" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT46" s="1">
         <v>0</v>
@@ -9867,7 +9868,7 @@
         <v>0</v>
       </c>
       <c r="AZ46" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA46" s="1">
         <v>0</v>
@@ -9879,7 +9880,7 @@
         <v>0</v>
       </c>
       <c r="BD46" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE46" s="1">
         <v>0</v>
@@ -9899,13 +9900,13 @@
         <v>14</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G47" s="1">
         <v>1</v>
@@ -9914,22 +9915,22 @@
         <v>0</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K47" s="1">
         <v>1</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O47" s="1">
         <v>0</v>
@@ -9956,10 +9957,10 @@
         <v>0</v>
       </c>
       <c r="W47" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X47" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y47" s="1">
         <v>0</v>
@@ -10022,7 +10023,7 @@
         <v>0</v>
       </c>
       <c r="AS47" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT47" s="1">
         <v>0</v>
@@ -10043,7 +10044,7 @@
         <v>0</v>
       </c>
       <c r="AZ47" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA47" s="1">
         <v>0</v>
@@ -10055,7 +10056,7 @@
         <v>0</v>
       </c>
       <c r="BD47" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE47" s="1">
         <v>0</v>
@@ -10075,13 +10076,13 @@
         <v>15</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G48" s="1">
         <v>1</v>
@@ -10090,22 +10091,22 @@
         <v>0</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K48" s="1">
         <v>1</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O48" s="1">
         <v>0</v>
@@ -10132,10 +10133,10 @@
         <v>0</v>
       </c>
       <c r="W48" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X48" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y48" s="1">
         <v>0</v>
@@ -10198,7 +10199,7 @@
         <v>0</v>
       </c>
       <c r="AS48" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT48" s="1">
         <v>0</v>
@@ -10219,7 +10220,7 @@
         <v>0</v>
       </c>
       <c r="AZ48" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA48" s="1">
         <v>0</v>
@@ -10231,7 +10232,7 @@
         <v>0</v>
       </c>
       <c r="BD48" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE48" s="1">
         <v>0</v>
@@ -10251,13 +10252,13 @@
         <v>16</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G49" s="1">
         <v>1</v>
@@ -10266,22 +10267,22 @@
         <v>0</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K49" s="1">
         <v>1</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O49" s="1">
         <v>0</v>
@@ -10308,10 +10309,10 @@
         <v>0</v>
       </c>
       <c r="W49" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X49" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y49" s="1">
         <v>0</v>
@@ -10374,7 +10375,7 @@
         <v>0</v>
       </c>
       <c r="AS49" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT49" s="1">
         <v>0</v>
@@ -10395,7 +10396,7 @@
         <v>0</v>
       </c>
       <c r="AZ49" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA49" s="1">
         <v>0</v>
@@ -10407,7 +10408,7 @@
         <v>0</v>
       </c>
       <c r="BD49" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE49" s="1">
         <v>0</v>
@@ -10427,13 +10428,13 @@
         <v>17</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G50" s="1">
         <v>1</v>
@@ -10442,22 +10443,22 @@
         <v>0</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K50" s="1">
         <v>1</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O50" s="1">
         <v>0</v>
@@ -10484,10 +10485,10 @@
         <v>0</v>
       </c>
       <c r="W50" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X50" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y50" s="1">
         <v>0</v>
@@ -10550,7 +10551,7 @@
         <v>0</v>
       </c>
       <c r="AS50" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT50" s="1">
         <v>0</v>
@@ -10571,7 +10572,7 @@
         <v>0</v>
       </c>
       <c r="AZ50" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA50" s="1">
         <v>0</v>
@@ -10583,7 +10584,7 @@
         <v>0</v>
       </c>
       <c r="BD50" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE50" s="1">
         <v>0</v>
@@ -10603,13 +10604,13 @@
         <v>18</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G51" s="1">
         <v>1</v>
@@ -10618,22 +10619,22 @@
         <v>0</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K51" s="1">
         <v>1</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M51" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O51" s="1">
         <v>0</v>
@@ -10660,10 +10661,10 @@
         <v>0</v>
       </c>
       <c r="W51" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X51" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y51" s="1">
         <v>0</v>
@@ -10726,7 +10727,7 @@
         <v>0</v>
       </c>
       <c r="AS51" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT51" s="1">
         <v>0</v>
@@ -10747,7 +10748,7 @@
         <v>0</v>
       </c>
       <c r="AZ51" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA51" s="1">
         <v>0</v>
@@ -10759,7 +10760,7 @@
         <v>0</v>
       </c>
       <c r="BD51" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE51" s="1">
         <v>0</v>
@@ -10779,13 +10780,13 @@
         <v>19</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G52" s="1">
         <v>1</v>
@@ -10794,22 +10795,22 @@
         <v>0</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K52" s="1">
         <v>1</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O52" s="1">
         <v>0</v>
@@ -10836,10 +10837,10 @@
         <v>0</v>
       </c>
       <c r="W52" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X52" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y52" s="1">
         <v>0</v>
@@ -10902,7 +10903,7 @@
         <v>0</v>
       </c>
       <c r="AS52" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT52" s="1">
         <v>0</v>
@@ -10923,7 +10924,7 @@
         <v>0</v>
       </c>
       <c r="AZ52" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA52" s="1">
         <v>0</v>
@@ -10935,7 +10936,7 @@
         <v>0</v>
       </c>
       <c r="BD52" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE52" s="1">
         <v>0</v>
@@ -10955,13 +10956,13 @@
         <v>20</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G53" s="1">
         <v>1</v>
@@ -10970,22 +10971,22 @@
         <v>0</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K53" s="1">
         <v>1</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O53" s="1">
         <v>0</v>
@@ -11012,10 +11013,10 @@
         <v>0</v>
       </c>
       <c r="W53" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X53" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y53" s="1">
         <v>0</v>
@@ -11078,7 +11079,7 @@
         <v>0</v>
       </c>
       <c r="AS53" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT53" s="1">
         <v>0</v>
@@ -11099,7 +11100,7 @@
         <v>0</v>
       </c>
       <c r="AZ53" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA53" s="1">
         <v>0</v>
@@ -11111,7 +11112,7 @@
         <v>0</v>
       </c>
       <c r="BD53" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE53" s="1">
         <v>0</v>
@@ -11131,13 +11132,13 @@
         <v>21</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G54" s="1">
         <v>1</v>
@@ -11146,22 +11147,22 @@
         <v>0</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K54" s="1">
         <v>1</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O54" s="1">
         <v>0</v>
@@ -11188,10 +11189,10 @@
         <v>0</v>
       </c>
       <c r="W54" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X54" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y54" s="1">
         <v>0</v>
@@ -11254,7 +11255,7 @@
         <v>0</v>
       </c>
       <c r="AS54" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT54" s="1">
         <v>0</v>
@@ -11275,7 +11276,7 @@
         <v>0</v>
       </c>
       <c r="AZ54" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA54" s="1">
         <v>0</v>
@@ -11287,7 +11288,7 @@
         <v>0</v>
       </c>
       <c r="BD54" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE54" s="1">
         <v>0</v>
@@ -11307,13 +11308,13 @@
         <v>22</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G55" s="1">
         <v>1</v>
@@ -11322,22 +11323,22 @@
         <v>0</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K55" s="1">
         <v>1</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O55" s="1">
         <v>0</v>
@@ -11364,10 +11365,10 @@
         <v>0</v>
       </c>
       <c r="W55" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X55" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y55" s="1">
         <v>0</v>
@@ -11430,7 +11431,7 @@
         <v>0</v>
       </c>
       <c r="AS55" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT55" s="1">
         <v>0</v>
@@ -11451,7 +11452,7 @@
         <v>0</v>
       </c>
       <c r="AZ55" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA55" s="1">
         <v>0</v>
@@ -11463,7 +11464,7 @@
         <v>0</v>
       </c>
       <c r="BD55" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE55" s="1">
         <v>0</v>
@@ -11483,13 +11484,13 @@
         <v>23</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G56" s="1">
         <v>1</v>
@@ -11498,22 +11499,22 @@
         <v>0</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K56" s="1">
         <v>1</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O56" s="1">
         <v>0</v>
@@ -11540,10 +11541,10 @@
         <v>0</v>
       </c>
       <c r="W56" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X56" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y56" s="1">
         <v>0</v>
@@ -11606,7 +11607,7 @@
         <v>0</v>
       </c>
       <c r="AS56" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT56" s="1">
         <v>0</v>
@@ -11627,7 +11628,7 @@
         <v>0</v>
       </c>
       <c r="AZ56" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA56" s="1">
         <v>0</v>
@@ -11639,7 +11640,7 @@
         <v>0</v>
       </c>
       <c r="BD56" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE56" s="1">
         <v>0</v>
@@ -11659,13 +11660,13 @@
         <v>24</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G57" s="1">
         <v>1</v>
@@ -11674,22 +11675,22 @@
         <v>0</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K57" s="1">
         <v>1</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O57" s="1">
         <v>0</v>
@@ -11716,10 +11717,10 @@
         <v>0</v>
       </c>
       <c r="W57" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X57" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y57" s="1">
         <v>0</v>
@@ -11782,7 +11783,7 @@
         <v>0</v>
       </c>
       <c r="AS57" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT57" s="1">
         <v>0</v>
@@ -11803,7 +11804,7 @@
         <v>0</v>
       </c>
       <c r="AZ57" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA57" s="1">
         <v>0</v>
@@ -11815,7 +11816,7 @@
         <v>0</v>
       </c>
       <c r="BD57" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE57" s="1">
         <v>0</v>
@@ -11835,13 +11836,13 @@
         <v>25</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G58" s="1">
         <v>1</v>
@@ -11850,22 +11851,22 @@
         <v>0</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K58" s="1">
         <v>1</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O58" s="1">
         <v>0</v>
@@ -11892,10 +11893,10 @@
         <v>0</v>
       </c>
       <c r="W58" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X58" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y58" s="1">
         <v>0</v>
@@ -11958,7 +11959,7 @@
         <v>0</v>
       </c>
       <c r="AS58" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT58" s="1">
         <v>0</v>
@@ -11979,7 +11980,7 @@
         <v>0</v>
       </c>
       <c r="AZ58" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA58" s="1">
         <v>0</v>
@@ -11991,7 +11992,7 @@
         <v>0</v>
       </c>
       <c r="BD58" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE58" s="1">
         <v>0</v>
@@ -12011,13 +12012,13 @@
         <v>26</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G59" s="1">
         <v>1</v>
@@ -12026,22 +12027,22 @@
         <v>0</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K59" s="1">
         <v>1</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O59" s="1">
         <v>0</v>
@@ -12068,10 +12069,10 @@
         <v>0</v>
       </c>
       <c r="W59" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X59" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y59" s="1">
         <v>0</v>
@@ -12134,7 +12135,7 @@
         <v>0</v>
       </c>
       <c r="AS59" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT59" s="1">
         <v>0</v>
@@ -12155,7 +12156,7 @@
         <v>0</v>
       </c>
       <c r="AZ59" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA59" s="1">
         <v>0</v>
@@ -12167,7 +12168,7 @@
         <v>0</v>
       </c>
       <c r="BD59" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE59" s="1">
         <v>0</v>
@@ -12187,13 +12188,13 @@
         <v>27</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G60" s="1">
         <v>1</v>
@@ -12202,22 +12203,22 @@
         <v>0</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K60" s="1">
         <v>1</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M60" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O60" s="1">
         <v>0</v>
@@ -12244,10 +12245,10 @@
         <v>0</v>
       </c>
       <c r="W60" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X60" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y60" s="1">
         <v>0</v>
@@ -12310,7 +12311,7 @@
         <v>0</v>
       </c>
       <c r="AS60" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT60" s="1">
         <v>0</v>
@@ -12331,7 +12332,7 @@
         <v>0</v>
       </c>
       <c r="AZ60" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA60" s="1">
         <v>0</v>
@@ -12343,7 +12344,7 @@
         <v>0</v>
       </c>
       <c r="BD60" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE60" s="1">
         <v>0</v>
@@ -12363,13 +12364,13 @@
         <v>28</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G61" s="1">
         <v>1</v>
@@ -12378,22 +12379,22 @@
         <v>0</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K61" s="1">
         <v>1</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M61" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O61" s="1">
         <v>0</v>
@@ -12420,10 +12421,10 @@
         <v>0</v>
       </c>
       <c r="W61" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X61" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y61" s="1">
         <v>0</v>
@@ -12486,7 +12487,7 @@
         <v>0</v>
       </c>
       <c r="AS61" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT61" s="1">
         <v>0</v>
@@ -12507,7 +12508,7 @@
         <v>0</v>
       </c>
       <c r="AZ61" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA61" s="1">
         <v>0</v>
@@ -12519,7 +12520,7 @@
         <v>0</v>
       </c>
       <c r="BD61" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE61" s="1">
         <v>0</v>
@@ -12539,13 +12540,13 @@
         <v>29</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G62" s="1">
         <v>1</v>
@@ -12554,22 +12555,22 @@
         <v>0</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K62" s="1">
         <v>1</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M62" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O62" s="1">
         <v>0</v>
@@ -12596,10 +12597,10 @@
         <v>0</v>
       </c>
       <c r="W62" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X62" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y62" s="1">
         <v>0</v>
@@ -12662,7 +12663,7 @@
         <v>0</v>
       </c>
       <c r="AS62" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT62" s="1">
         <v>0</v>
@@ -12683,7 +12684,7 @@
         <v>0</v>
       </c>
       <c r="AZ62" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA62" s="1">
         <v>0</v>
@@ -12695,7 +12696,7 @@
         <v>0</v>
       </c>
       <c r="BD62" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE62" s="1">
         <v>0</v>
@@ -12715,13 +12716,13 @@
         <v>30</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G63" s="1">
         <v>1</v>
@@ -12730,22 +12731,22 @@
         <v>0</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K63" s="1">
         <v>1</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M63" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O63" s="1">
         <v>0</v>
@@ -12772,10 +12773,10 @@
         <v>0</v>
       </c>
       <c r="W63" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X63" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y63" s="1">
         <v>0</v>
@@ -12838,7 +12839,7 @@
         <v>0</v>
       </c>
       <c r="AS63" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT63" s="1">
         <v>0</v>
@@ -12859,7 +12860,7 @@
         <v>0</v>
       </c>
       <c r="AZ63" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA63" s="1">
         <v>0</v>
@@ -12871,7 +12872,7 @@
         <v>0</v>
       </c>
       <c r="BD63" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE63" s="1">
         <v>0</v>
@@ -12891,14 +12892,14 @@
         <v>2</v>
       </c>
       <c r="D64" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="E64" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="E64" s="12" t="s">
+      <c r="F64" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="F64" s="12" t="s">
-        <v>166</v>
-      </c>
       <c r="G64" s="12">
         <v>0</v>
       </c>
@@ -12906,7 +12907,7 @@
         <v>0</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J64" s="4">
         <v>43400002</v>
@@ -12915,10 +12916,10 @@
         <v>5</v>
       </c>
       <c r="L64" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="M64" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="M64" s="12" t="s">
-        <v>121</v>
       </c>
       <c r="N64" s="12">
         <v>0</v>
@@ -12948,10 +12949,10 @@
         <v>0</v>
       </c>
       <c r="W64" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X64" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y64" s="12">
         <v>0</v>
@@ -13014,7 +13015,7 @@
         <v>2</v>
       </c>
       <c r="AS64" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT64" s="1">
         <v>0</v>
@@ -13035,7 +13036,7 @@
         <v>0</v>
       </c>
       <c r="AZ64" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA64" s="10">
         <v>0</v>
@@ -13047,7 +13048,7 @@
         <v>0</v>
       </c>
       <c r="BD64" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE64" s="4">
         <v>43400002</v>
@@ -13067,37 +13068,37 @@
         <v>1</v>
       </c>
       <c r="D65" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="F65" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="F65" s="1" t="s">
+      <c r="G65" s="1">
+        <v>1</v>
+      </c>
+      <c r="H65" s="1">
+        <v>0</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J65" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="G65" s="1">
-        <v>1</v>
-      </c>
-      <c r="H65" s="1">
-        <v>0</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J65" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="K65" s="1">
         <v>1</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M65" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N65" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O65" s="1">
         <v>0</v>
@@ -13124,10 +13125,10 @@
         <v>0</v>
       </c>
       <c r="W65" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X65" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y65" s="1">
         <v>0</v>
@@ -13190,7 +13191,7 @@
         <v>0</v>
       </c>
       <c r="AS65" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT65" s="1">
         <v>0</v>
@@ -13211,7 +13212,7 @@
         <v>0</v>
       </c>
       <c r="AZ65" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA65" s="1">
         <v>0</v>
@@ -13223,7 +13224,7 @@
         <v>0</v>
       </c>
       <c r="BD65" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE65" s="1">
         <v>0</v>
@@ -13243,37 +13244,37 @@
         <v>1</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E66" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G66" s="1">
+        <v>1</v>
+      </c>
+      <c r="H66" s="1">
+        <v>0</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J66" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="F66" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="G66" s="1">
-        <v>1</v>
-      </c>
-      <c r="H66" s="1">
-        <v>0</v>
-      </c>
-      <c r="I66" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J66" s="13" t="s">
-        <v>202</v>
-      </c>
       <c r="K66" s="1">
         <v>1</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O66" s="1">
         <v>0</v>
@@ -13300,10 +13301,10 @@
         <v>0</v>
       </c>
       <c r="W66" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X66" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y66" s="1">
         <v>0</v>
@@ -13366,7 +13367,7 @@
         <v>0</v>
       </c>
       <c r="AS66" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT66" s="1">
         <v>0</v>
@@ -13387,7 +13388,7 @@
         <v>0</v>
       </c>
       <c r="AZ66" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA66" s="1">
         <v>0</v>
@@ -13399,7 +13400,7 @@
         <v>0</v>
       </c>
       <c r="BD66" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE66" s="1">
         <v>0</v>
@@ -13419,13 +13420,13 @@
         <v>1</v>
       </c>
       <c r="D67" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E67" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="E67" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="F67" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G67" s="1">
         <v>1</v>
@@ -13434,7 +13435,7 @@
         <v>0</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J67" s="1">
         <v>44300001</v>
@@ -13443,13 +13444,13 @@
         <v>1</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O67" s="1">
         <v>0</v>
@@ -13476,10 +13477,10 @@
         <v>0</v>
       </c>
       <c r="W67" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X67" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y67" s="1">
         <v>0</v>
@@ -13542,7 +13543,7 @@
         <v>0</v>
       </c>
       <c r="AS67" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT67" s="1">
         <v>0</v>
@@ -13563,7 +13564,7 @@
         <v>0</v>
       </c>
       <c r="AZ67" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA67" s="1">
         <v>0</v>
@@ -13575,7 +13576,7 @@
         <v>0</v>
       </c>
       <c r="BD67" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE67" s="1">
         <v>0</v>
@@ -13595,13 +13596,13 @@
         <v>1</v>
       </c>
       <c r="D68" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E68" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="E68" s="1" t="s">
-        <v>175</v>
-      </c>
       <c r="F68" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G68" s="1">
         <v>1</v>
@@ -13610,7 +13611,7 @@
         <v>0</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J68" s="1">
         <v>38500001</v>
@@ -13619,13 +13620,13 @@
         <v>1</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M68" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O68" s="1">
         <v>0</v>
@@ -13652,10 +13653,10 @@
         <v>0</v>
       </c>
       <c r="W68" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X68" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y68" s="1">
         <v>0</v>
@@ -13718,7 +13719,7 @@
         <v>0</v>
       </c>
       <c r="AS68" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT68" s="1">
         <v>0</v>
@@ -13739,7 +13740,7 @@
         <v>0</v>
       </c>
       <c r="AZ68" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA68" s="1">
         <v>0</v>
@@ -13751,7 +13752,7 @@
         <v>0</v>
       </c>
       <c r="BD68" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE68" s="1">
         <v>0</v>
@@ -13771,14 +13772,14 @@
         <v>1</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E69" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F69" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="F69" s="1" t="s">
-        <v>170</v>
-      </c>
       <c r="G69" s="1">
         <v>0</v>
       </c>
@@ -13786,7 +13787,7 @@
         <v>0</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J69" s="1">
         <v>45100001</v>
@@ -13795,13 +13796,13 @@
         <v>1</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M69" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O69" s="1">
         <v>0</v>
@@ -13819,7 +13820,7 @@
         <v>0</v>
       </c>
       <c r="T69" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U69" s="1">
         <v>0</v>
@@ -13828,10 +13829,10 @@
         <v>0</v>
       </c>
       <c r="W69" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X69" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y69" s="1">
         <v>0</v>
@@ -13894,7 +13895,7 @@
         <v>0</v>
       </c>
       <c r="AS69" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT69" s="1">
         <v>0</v>
@@ -13915,7 +13916,7 @@
         <v>0</v>
       </c>
       <c r="AZ69" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA69" s="1">
         <v>0</v>
@@ -13927,7 +13928,7 @@
         <v>0</v>
       </c>
       <c r="BD69" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE69" s="1">
         <v>0</v>
@@ -13947,37 +13948,37 @@
         <v>1</v>
       </c>
       <c r="D70" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E70" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="E70" s="1" t="s">
+      <c r="F70" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G70" s="1">
+        <v>0</v>
+      </c>
+      <c r="H70" s="1">
+        <v>0</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J70" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="F70" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="G70" s="1">
-        <v>0</v>
-      </c>
-      <c r="H70" s="1">
-        <v>0</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J70" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="K70" s="1">
         <v>1</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M70" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O70" s="1">
         <v>0</v>
@@ -14004,10 +14005,10 @@
         <v>0</v>
       </c>
       <c r="W70" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X70" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y70" s="1">
         <v>0</v>
@@ -14070,7 +14071,7 @@
         <v>0</v>
       </c>
       <c r="AS70" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT70" s="1">
         <v>0</v>
@@ -14091,7 +14092,7 @@
         <v>0</v>
       </c>
       <c r="AZ70" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA70" s="1">
         <v>0</v>
@@ -14103,7 +14104,7 @@
         <v>0</v>
       </c>
       <c r="BD70" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE70" s="1">
         <v>0</v>
@@ -14123,13 +14124,13 @@
         <v>1</v>
       </c>
       <c r="D71" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E71" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="E71" s="1" t="s">
-        <v>178</v>
-      </c>
       <c r="F71" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G71" s="1">
         <v>0</v>
@@ -14138,7 +14139,7 @@
         <v>0</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J71" s="1">
         <v>44500001</v>
@@ -14147,13 +14148,13 @@
         <v>1</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M71" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O71" s="1">
         <v>0</v>
@@ -14180,10 +14181,10 @@
         <v>0</v>
       </c>
       <c r="W71" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X71" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y71" s="1">
         <v>0</v>
@@ -14246,7 +14247,7 @@
         <v>0</v>
       </c>
       <c r="AS71" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT71" s="1">
         <v>0</v>
@@ -14267,7 +14268,7 @@
         <v>0</v>
       </c>
       <c r="AZ71" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA71" s="1">
         <v>0</v>
@@ -14279,7 +14280,7 @@
         <v>0</v>
       </c>
       <c r="BD71" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE71" s="1">
         <v>0</v>
@@ -14299,13 +14300,13 @@
         <v>1</v>
       </c>
       <c r="D72" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E72" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E72" s="1" t="s">
-        <v>180</v>
-      </c>
       <c r="F72" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G72" s="1">
         <v>0</v>
@@ -14314,22 +14315,22 @@
         <v>0</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K72" s="1">
         <v>1</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M72" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O72" s="1">
         <v>0</v>
@@ -14356,10 +14357,10 @@
         <v>0</v>
       </c>
       <c r="W72" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X72" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y72" s="1">
         <v>0</v>
@@ -14422,7 +14423,7 @@
         <v>0</v>
       </c>
       <c r="AS72" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT72" s="1">
         <v>0</v>
@@ -14443,7 +14444,7 @@
         <v>0</v>
       </c>
       <c r="AZ72" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA72" s="1">
         <v>0</v>
@@ -14455,7 +14456,7 @@
         <v>0</v>
       </c>
       <c r="BD72" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE72" s="1">
         <v>0</v>
@@ -14475,13 +14476,13 @@
         <v>1</v>
       </c>
       <c r="D73" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E73" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="E73" s="1" t="s">
-        <v>182</v>
-      </c>
       <c r="F73" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G73" s="1">
         <v>0</v>
@@ -14490,7 +14491,7 @@
         <v>0</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J73" s="1">
         <v>45600001</v>
@@ -14499,13 +14500,13 @@
         <v>1</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M73" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N73" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O73" s="1">
         <v>0</v>
@@ -14532,10 +14533,10 @@
         <v>0</v>
       </c>
       <c r="W73" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X73" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y73" s="1">
         <v>0</v>
@@ -14598,7 +14599,7 @@
         <v>0</v>
       </c>
       <c r="AS73" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT73" s="1">
         <v>0</v>
@@ -14619,7 +14620,7 @@
         <v>0</v>
       </c>
       <c r="AZ73" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA73" s="1">
         <v>0</v>
@@ -14631,7 +14632,7 @@
         <v>0</v>
       </c>
       <c r="BD73" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE73" s="1">
         <v>0</v>
@@ -14651,13 +14652,13 @@
         <v>1</v>
       </c>
       <c r="D74" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E74" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="E74" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="F74" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G74" s="1">
         <v>1</v>
@@ -14666,7 +14667,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J74" s="1">
         <v>44400001</v>
@@ -14675,13 +14676,13 @@
         <v>1</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M74" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N74" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O74" s="1">
         <v>0</v>
@@ -14708,10 +14709,10 @@
         <v>0</v>
       </c>
       <c r="W74" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X74" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y74" s="1">
         <v>0</v>
@@ -14774,7 +14775,7 @@
         <v>0</v>
       </c>
       <c r="AS74" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT74" s="1">
         <v>0</v>
@@ -14795,7 +14796,7 @@
         <v>0</v>
       </c>
       <c r="AZ74" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA74" s="1">
         <v>0</v>
@@ -14807,7 +14808,7 @@
         <v>0</v>
       </c>
       <c r="BD74" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE74" s="1">
         <v>0</v>
@@ -14827,13 +14828,13 @@
         <v>1</v>
       </c>
       <c r="D75" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E75" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="E75" s="12" t="s">
-        <v>186</v>
-      </c>
       <c r="F75" s="12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G75" s="12">
         <v>0</v>
@@ -14842,7 +14843,7 @@
         <v>0</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J75" s="4">
         <v>48200001</v>
@@ -14851,10 +14852,10 @@
         <v>5</v>
       </c>
       <c r="L75" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="M75" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="M75" s="12" t="s">
-        <v>121</v>
       </c>
       <c r="N75" s="12">
         <v>0</v>
@@ -14884,10 +14885,10 @@
         <v>0</v>
       </c>
       <c r="W75" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X75" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y75" s="12">
         <v>0</v>
@@ -14950,7 +14951,7 @@
         <v>2</v>
       </c>
       <c r="AS75" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT75" s="1">
         <v>0</v>
@@ -14971,7 +14972,7 @@
         <v>0</v>
       </c>
       <c r="AZ75" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA75" s="10">
         <v>0</v>
@@ -14983,7 +14984,7 @@
         <v>0</v>
       </c>
       <c r="BD75" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE75" s="4">
         <v>0</v>
@@ -15003,14 +15004,14 @@
         <v>1</v>
       </c>
       <c r="D76" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="E76" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="E76" s="12" t="s">
+      <c r="F76" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="F76" s="12" t="s">
-        <v>166</v>
-      </c>
       <c r="G76" s="12">
         <v>0</v>
       </c>
@@ -15018,7 +15019,7 @@
         <v>0</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J76" s="4">
         <v>48300001</v>
@@ -15027,10 +15028,10 @@
         <v>5</v>
       </c>
       <c r="L76" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="M76" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="M76" s="12" t="s">
-        <v>121</v>
       </c>
       <c r="N76" s="12">
         <v>0</v>
@@ -15060,10 +15061,10 @@
         <v>0</v>
       </c>
       <c r="W76" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X76" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y76" s="12">
         <v>0</v>
@@ -15126,7 +15127,7 @@
         <v>2</v>
       </c>
       <c r="AS76" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT76" s="1">
         <v>0</v>
@@ -15147,7 +15148,7 @@
         <v>0</v>
       </c>
       <c r="AZ76" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA76" s="10">
         <v>0</v>
@@ -15159,7 +15160,7 @@
         <v>0</v>
       </c>
       <c r="BD76" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE76" s="4">
         <v>0</v>
@@ -15179,13 +15180,13 @@
         <v>2</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F77" s="12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G77" s="12">
         <v>0</v>
@@ -15194,7 +15195,7 @@
         <v>0</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J77" s="4">
         <v>48300002</v>
@@ -15203,10 +15204,10 @@
         <v>5</v>
       </c>
       <c r="L77" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="M77" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="M77" s="12" t="s">
-        <v>121</v>
       </c>
       <c r="N77" s="12">
         <v>0</v>
@@ -15236,10 +15237,10 @@
         <v>0</v>
       </c>
       <c r="W77" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X77" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y77" s="12">
         <v>0</v>
@@ -15302,7 +15303,7 @@
         <v>2</v>
       </c>
       <c r="AS77" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT77" s="1">
         <v>0</v>
@@ -15323,7 +15324,7 @@
         <v>0</v>
       </c>
       <c r="AZ77" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA77" s="10">
         <v>0</v>
@@ -15335,7 +15336,7 @@
         <v>0</v>
       </c>
       <c r="BD77" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE77" s="4">
         <v>0</v>
@@ -15355,13 +15356,13 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F78" s="12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G78" s="12">
         <v>0</v>
@@ -15370,7 +15371,7 @@
         <v>0</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J78" s="4">
         <v>48300003</v>
@@ -15379,10 +15380,10 @@
         <v>5</v>
       </c>
       <c r="L78" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="M78" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="M78" s="12" t="s">
-        <v>121</v>
       </c>
       <c r="N78" s="12">
         <v>0</v>
@@ -15412,10 +15413,10 @@
         <v>0</v>
       </c>
       <c r="W78" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X78" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y78" s="12">
         <v>0</v>
@@ -15478,7 +15479,7 @@
         <v>2</v>
       </c>
       <c r="AS78" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT78" s="1">
         <v>0</v>
@@ -15499,7 +15500,7 @@
         <v>0</v>
       </c>
       <c r="AZ78" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA78" s="10">
         <v>0</v>
@@ -15511,7 +15512,7 @@
         <v>0</v>
       </c>
       <c r="BD78" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE78" s="4">
         <v>0</v>
@@ -15531,13 +15532,13 @@
         <v>4</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F79" s="12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G79" s="12">
         <v>0</v>
@@ -15546,7 +15547,7 @@
         <v>0</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J79" s="4">
         <v>48300004</v>
@@ -15555,10 +15556,10 @@
         <v>5</v>
       </c>
       <c r="L79" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="M79" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="M79" s="12" t="s">
-        <v>121</v>
       </c>
       <c r="N79" s="12">
         <v>0</v>
@@ -15588,10 +15589,10 @@
         <v>0</v>
       </c>
       <c r="W79" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X79" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y79" s="12">
         <v>0</v>
@@ -15654,7 +15655,7 @@
         <v>2</v>
       </c>
       <c r="AS79" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT79" s="1">
         <v>0</v>
@@ -15675,7 +15676,7 @@
         <v>0</v>
       </c>
       <c r="AZ79" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA79" s="10">
         <v>0</v>
@@ -15687,7 +15688,7 @@
         <v>0</v>
       </c>
       <c r="BD79" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE79" s="4">
         <v>0</v>
@@ -15707,13 +15708,13 @@
         <v>5</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F80" s="12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G80" s="12">
         <v>0</v>
@@ -15722,7 +15723,7 @@
         <v>0</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J80" s="4">
         <v>48300005</v>
@@ -15731,10 +15732,10 @@
         <v>5</v>
       </c>
       <c r="L80" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="M80" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="M80" s="12" t="s">
-        <v>121</v>
       </c>
       <c r="N80" s="12">
         <v>0</v>
@@ -15764,10 +15765,10 @@
         <v>0</v>
       </c>
       <c r="W80" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X80" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y80" s="12">
         <v>0</v>
@@ -15830,7 +15831,7 @@
         <v>2</v>
       </c>
       <c r="AS80" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT80" s="1">
         <v>0</v>
@@ -15851,7 +15852,7 @@
         <v>0</v>
       </c>
       <c r="AZ80" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA80" s="10">
         <v>0</v>
@@ -15863,7 +15864,7 @@
         <v>0</v>
       </c>
       <c r="BD80" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE80" s="4">
         <v>0</v>
@@ -15883,22 +15884,22 @@
         <v>6</v>
       </c>
       <c r="D81" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E81" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="F81" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="G81" s="12">
+        <v>0</v>
+      </c>
+      <c r="H81" s="12">
+        <v>0</v>
+      </c>
+      <c r="I81" s="4" t="s">
         <v>191</v>
-      </c>
-      <c r="E81" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="F81" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="G81" s="12">
-        <v>0</v>
-      </c>
-      <c r="H81" s="12">
-        <v>0</v>
-      </c>
-      <c r="I81" s="4" t="s">
-        <v>192</v>
       </c>
       <c r="J81" s="4">
         <v>48300006</v>
@@ -15907,10 +15908,10 @@
         <v>5</v>
       </c>
       <c r="L81" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="M81" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="M81" s="12" t="s">
-        <v>121</v>
       </c>
       <c r="N81" s="12">
         <v>0</v>
@@ -15940,10 +15941,10 @@
         <v>0</v>
       </c>
       <c r="W81" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X81" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y81" s="12">
         <v>0</v>
@@ -16006,7 +16007,7 @@
         <v>2</v>
       </c>
       <c r="AS81" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT81" s="1">
         <v>0</v>
@@ -16027,7 +16028,7 @@
         <v>0</v>
       </c>
       <c r="AZ81" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA81" s="10">
         <v>0</v>
@@ -16039,7 +16040,7 @@
         <v>0</v>
       </c>
       <c r="BD81" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE81" s="4">
         <v>0</v>
@@ -16059,37 +16060,37 @@
         <v>1</v>
       </c>
       <c r="D82" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="E82" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="E82" s="1" t="s">
+      <c r="F82" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G82" s="1">
+        <v>0</v>
+      </c>
+      <c r="H82" s="1">
+        <v>0</v>
+      </c>
+      <c r="I82" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="J82" s="4" t="s">
         <v>199</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="G82" s="1">
-        <v>0</v>
-      </c>
-      <c r="H82" s="1">
-        <v>0</v>
-      </c>
-      <c r="I82" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="J82" s="4" t="s">
-        <v>200</v>
       </c>
       <c r="K82" s="1">
         <v>5</v>
       </c>
       <c r="L82" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="M82" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="M82" s="12" t="s">
+      <c r="N82" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="N82" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="O82" s="1">
         <v>0</v>
@@ -16116,10 +16117,10 @@
         <v>0</v>
       </c>
       <c r="W82" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X82" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y82" s="1">
         <v>0</v>
@@ -16182,7 +16183,7 @@
         <v>0</v>
       </c>
       <c r="AS82" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AT82" s="1">
         <v>0</v>
@@ -16203,7 +16204,7 @@
         <v>0</v>
       </c>
       <c r="AZ82" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA82" s="1">
         <v>0</v>
@@ -16215,7 +16216,7 @@
         <v>0</v>
       </c>
       <c r="BD82" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE82" s="1">
         <v>0</v>
@@ -16225,7 +16226,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:BE63" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="11" type="noConversion"/>
   <dataValidations disablePrompts="1" count="2">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="-1，没有跳转_x000a_0，程序预留_x000a_1，探索关卡跳转  _x000a_2，建筑跳转_x000a_3，商城预留_x000a_4，网页跳转预留_x000a_一个道具多个跳转类型，则填list" sqref="AK4" xr:uid="{00000000-0002-0000-0000-000000000000}"/>

--- a/servers/maze_main_server/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B668B4-FDA4-4BF5-8A62-97187C8570CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EEA41D3-805A-48D2-8650-559B3E90DFAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13820,7 +13820,7 @@
         <v>0</v>
       </c>
       <c r="T69" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U69" s="1">
         <v>0</v>
@@ -13996,7 +13996,7 @@
         <v>0</v>
       </c>
       <c r="T70" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U70" s="1">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EEA41D3-805A-48D2-8650-559B3E90DFAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E188E3E-D42B-473D-9E5E-441B65750603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1167,10 +1167,6 @@
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
-    <t>金币堆</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
     <t>强化水晶</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
@@ -1184,6 +1180,10 @@
   </si>
   <si>
     <t>is_bag</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>金币</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -2204,7 +2204,7 @@
         <v>34</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="U3" s="6" t="s">
         <v>35</v>
@@ -13244,7 +13244,7 @@
         <v>1</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>200</v>
@@ -13948,10 +13948,10 @@
         <v>1</v>
       </c>
       <c r="D70" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E70" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>204</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>169</v>
@@ -13966,7 +13966,7 @@
         <v>191</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K70" s="1">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E188E3E-D42B-473D-9E5E-441B65750603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1E93C29-C067-4E32-8B94-797596A22E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
